--- a/excel/Building A B Lighting New.xlsx
+++ b/excel/Building A B Lighting New.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weiwi\OneDrive\Documents\GitHub\Alpha_Design_17\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lsen906\Documents\Alpha_Design_17\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A209C7-B144-4432-A7A4-DC626B9110FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D764F81-86BA-4BC3-A730-A242110B5A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Building A" sheetId="1" r:id="rId1"/>
@@ -26,17 +26,16 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="188">
   <si>
     <t>Building A — Lighting Place Schedule</t>
   </si>
@@ -59,6 +58,9 @@
     <t>Target Maintained lx</t>
   </si>
   <si>
+    <t>Initial Target lx (MF 0.8)</t>
+  </si>
+  <si>
     <t>g1 Uniformity Target</t>
   </si>
   <si>
@@ -593,14 +595,17 @@
     <t>Existing Luminaire (2)</t>
   </si>
   <si>
-    <t>Initial Target lx (MF 0.76)</t>
+    <t>Existing Qty (2)</t>
+  </si>
+  <si>
+    <t>Existing W each (2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -619,6 +624,10 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -1003,7 +1012,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X36"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -1022,7 +1031,7 @@
     <col min="21" max="21" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="20.65">
+    <row r="1" spans="1:24" ht="20.25">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1056,7 @@
       <c r="T1" s="27"/>
       <c r="U1" s="27"/>
     </row>
-    <row r="2" spans="1:24" ht="41.65">
+    <row r="2" spans="1:24" ht="45">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1067,72 +1076,72 @@
         <v>6</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="25.5">
       <c r="A3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="16">
         <v>0</v>
@@ -1141,23 +1150,23 @@
         <v>80</v>
       </c>
       <c r="G3" s="18">
-        <f>ROUND(F3/0.76,0)</f>
-        <v>105</v>
+        <f t="shared" ref="G3:G36" si="0">ROUND(F3/0.8,0)</f>
+        <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="9">
         <v>1</v>
@@ -1173,7 +1182,7 @@
         <v>72</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T3" s="9"/>
       <c r="U3" s="20"/>
@@ -1182,25 +1191,25 @@
         <v/>
       </c>
       <c r="W3" s="20" t="str">
-        <f t="shared" ref="W3:W36" si="0">IF(OR(R3="",V3=""),"",R3-V3)</f>
+        <f t="shared" ref="W3:W36" si="1">IF(OR(R3="",V3=""),"",R3-V3)</f>
         <v/>
       </c>
       <c r="X3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="25.5">
       <c r="A4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="16">
         <v>0</v>
@@ -1209,23 +1218,23 @@
         <v>40</v>
       </c>
       <c r="G4" s="18">
-        <f t="shared" ref="G4:G36" si="1">ROUND(F4/0.76,0)</f>
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" s="9">
         <v>2</v>
@@ -1234,7 +1243,7 @@
         <v>72</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P4" s="25">
         <v>5</v>
@@ -1248,7 +1257,7 @@
         <v>288</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T4" s="9"/>
       <c r="U4" s="20"/>
@@ -1257,25 +1266,25 @@
         <v/>
       </c>
       <c r="W4" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X4" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="25.5">
       <c r="A5" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" s="16">
         <v>0</v>
@@ -1284,23 +1293,23 @@
         <v>80</v>
       </c>
       <c r="G5" s="18">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M5" s="9">
         <v>1</v>
@@ -1316,7 +1325,7 @@
         <v>72</v>
       </c>
       <c r="S5" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="20"/>
@@ -1325,25 +1334,25 @@
         <v/>
       </c>
       <c r="W5" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="25.5">
       <c r="A6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="16">
         <v>0</v>
@@ -1352,23 +1361,23 @@
         <v>80</v>
       </c>
       <c r="G6" s="18">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M6" s="9">
         <v>1</v>
@@ -1384,7 +1393,7 @@
         <v>72</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T6" s="9"/>
       <c r="U6" s="20"/>
@@ -1393,25 +1402,25 @@
         <v/>
       </c>
       <c r="W6" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="25.5">
       <c r="A7" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="16">
         <v>0</v>
@@ -1420,23 +1429,23 @@
         <v>80</v>
       </c>
       <c r="G7" s="18">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M7" s="9">
         <v>1</v>
@@ -1452,7 +1461,7 @@
         <v>72</v>
       </c>
       <c r="S7" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T7" s="9"/>
       <c r="U7" s="20"/>
@@ -1461,25 +1470,25 @@
         <v/>
       </c>
       <c r="W7" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="25.5">
       <c r="A8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="16">
         <v>0.7</v>
@@ -1488,23 +1497,23 @@
         <v>320</v>
       </c>
       <c r="G8" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M8" s="9">
         <v>2</v>
@@ -1520,7 +1529,7 @@
         <v>288</v>
       </c>
       <c r="S8" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T8" s="9"/>
       <c r="U8" s="20"/>
@@ -1529,25 +1538,25 @@
         <v/>
       </c>
       <c r="W8" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X8" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="25.5">
       <c r="A9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" s="16">
         <v>0.7</v>
@@ -1556,23 +1565,23 @@
         <v>320</v>
       </c>
       <c r="G9" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M9" s="9">
         <v>2</v>
@@ -1588,7 +1597,7 @@
         <v>288</v>
       </c>
       <c r="S9" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T9" s="9"/>
       <c r="U9" s="20"/>
@@ -1597,25 +1606,25 @@
         <v/>
       </c>
       <c r="W9" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X9" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="25.5">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="16">
         <v>0</v>
@@ -1624,23 +1633,23 @@
         <v>40</v>
       </c>
       <c r="G10" s="18">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M10" s="9">
         <v>4</v>
@@ -1649,7 +1658,7 @@
         <v>72</v>
       </c>
       <c r="O10" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P10" s="25">
         <v>4</v>
@@ -1663,7 +1672,7 @@
         <v>432</v>
       </c>
       <c r="S10" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T10" s="9"/>
       <c r="U10" s="20"/>
@@ -1672,25 +1681,25 @@
         <v/>
       </c>
       <c r="W10" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X10" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="25.5">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" s="16">
         <v>0.7</v>
@@ -1699,23 +1708,23 @@
         <v>320</v>
       </c>
       <c r="G11" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M11" s="9">
         <v>2</v>
@@ -1731,7 +1740,7 @@
         <v>288</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T11" s="9"/>
       <c r="U11" s="20"/>
@@ -1740,25 +1749,25 @@
         <v/>
       </c>
       <c r="W11" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X11" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="25.5">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" s="16">
         <v>0.7</v>
@@ -1767,23 +1776,23 @@
         <v>320</v>
       </c>
       <c r="G12" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M12" s="9">
         <v>4</v>
@@ -1799,7 +1808,7 @@
         <v>576</v>
       </c>
       <c r="S12" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T12" s="9"/>
       <c r="U12" s="20"/>
@@ -1808,25 +1817,25 @@
         <v/>
       </c>
       <c r="W12" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="25.5">
       <c r="A13" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E13" s="16">
         <v>0.7</v>
@@ -1835,23 +1844,23 @@
         <v>320</v>
       </c>
       <c r="G13" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M13" s="9">
         <v>4</v>
@@ -1867,7 +1876,7 @@
         <v>576</v>
       </c>
       <c r="S13" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T13" s="9"/>
       <c r="U13" s="20"/>
@@ -1876,25 +1885,25 @@
         <v/>
       </c>
       <c r="W13" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X13" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="25.5">
       <c r="A14" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="E14" s="16">
         <v>0.7</v>
@@ -1903,23 +1912,23 @@
         <v>320</v>
       </c>
       <c r="G14" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M14" s="9">
         <v>6</v>
@@ -1935,7 +1944,7 @@
         <v>864</v>
       </c>
       <c r="S14" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T14" s="9"/>
       <c r="U14" s="20"/>
@@ -1944,25 +1953,25 @@
         <v/>
       </c>
       <c r="W14" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X14" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="25.5">
       <c r="A15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" s="16">
         <v>0.7</v>
@@ -1971,23 +1980,23 @@
         <v>320</v>
       </c>
       <c r="G15" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M15" s="9">
         <v>3</v>
@@ -2003,7 +2012,7 @@
         <v>432</v>
       </c>
       <c r="S15" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T15" s="9"/>
       <c r="U15" s="20"/>
@@ -2012,25 +2021,25 @@
         <v/>
       </c>
       <c r="W15" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X15" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="25.5">
       <c r="A16" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E16" s="16">
         <v>0.7</v>
@@ -2039,23 +2048,23 @@
         <v>160</v>
       </c>
       <c r="G16" s="18">
-        <f t="shared" si="1"/>
-        <v>211</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M16" s="9">
         <v>3</v>
@@ -2071,7 +2080,7 @@
         <v>432</v>
       </c>
       <c r="S16" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T16" s="9"/>
       <c r="U16" s="20"/>
@@ -2080,25 +2089,25 @@
         <v/>
       </c>
       <c r="W16" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X16" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="25.5">
       <c r="A17" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="16">
         <v>0</v>
@@ -2107,23 +2116,23 @@
         <v>80</v>
       </c>
       <c r="G17" s="18">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M17" s="9">
         <v>1</v>
@@ -2139,7 +2148,7 @@
         <v>72</v>
       </c>
       <c r="S17" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T17" s="9"/>
       <c r="U17" s="20"/>
@@ -2148,25 +2157,25 @@
         <v/>
       </c>
       <c r="W17" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X17" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="25.5">
       <c r="A18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="16">
         <v>0</v>
@@ -2175,23 +2184,23 @@
         <v>40</v>
       </c>
       <c r="G18" s="18">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M18" s="9">
         <v>4</v>
@@ -2207,7 +2216,7 @@
         <v>288</v>
       </c>
       <c r="S18" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T18" s="9"/>
       <c r="U18" s="20"/>
@@ -2216,25 +2225,25 @@
         <v/>
       </c>
       <c r="W18" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X18" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="25.5">
       <c r="A19" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19" s="16">
         <v>0.7</v>
@@ -2243,23 +2252,23 @@
         <v>320</v>
       </c>
       <c r="G19" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M19" s="9">
         <v>2</v>
@@ -2275,7 +2284,7 @@
         <v>288</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T19" s="9"/>
       <c r="U19" s="20"/>
@@ -2284,25 +2293,25 @@
         <v/>
       </c>
       <c r="W19" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X19" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="25.5">
       <c r="A20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" s="16">
         <v>0.7</v>
@@ -2311,23 +2320,23 @@
         <v>320</v>
       </c>
       <c r="G20" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M20" s="9">
         <v>7</v>
@@ -2343,7 +2352,7 @@
         <v>1008</v>
       </c>
       <c r="S20" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T20" s="9"/>
       <c r="U20" s="20"/>
@@ -2352,25 +2361,25 @@
         <v/>
       </c>
       <c r="W20" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="25.5">
       <c r="A21" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21" s="16">
         <v>0</v>
@@ -2379,23 +2388,23 @@
         <v>40</v>
       </c>
       <c r="G21" s="18">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M21" s="9">
         <v>1</v>
@@ -2411,7 +2420,7 @@
         <v>72</v>
       </c>
       <c r="S21" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T21" s="9"/>
       <c r="U21" s="20"/>
@@ -2420,25 +2429,25 @@
         <v/>
       </c>
       <c r="W21" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X21" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="25.5">
       <c r="A22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E22" s="16">
         <v>0</v>
@@ -2447,23 +2456,23 @@
         <v>80</v>
       </c>
       <c r="G22" s="18">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M22" s="9">
         <v>2</v>
@@ -2479,7 +2488,7 @@
         <v>144</v>
       </c>
       <c r="S22" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T22" s="9"/>
       <c r="U22" s="20"/>
@@ -2488,25 +2497,25 @@
         <v/>
       </c>
       <c r="W22" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X22" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="25.5">
       <c r="A23" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E23" s="16">
         <v>0.7</v>
@@ -2515,23 +2524,23 @@
         <v>320</v>
       </c>
       <c r="G23" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L23" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M23" s="9">
         <v>6</v>
@@ -2547,7 +2556,7 @@
         <v>864</v>
       </c>
       <c r="S23" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T23" s="9"/>
       <c r="U23" s="20"/>
@@ -2556,25 +2565,25 @@
         <v/>
       </c>
       <c r="W23" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X23" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="25.5">
       <c r="A24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E24" s="16">
         <v>0.7</v>
@@ -2583,23 +2592,23 @@
         <v>320</v>
       </c>
       <c r="G24" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M24" s="9">
         <v>4</v>
@@ -2615,7 +2624,7 @@
         <v>576</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="20"/>
@@ -2624,25 +2633,25 @@
         <v/>
       </c>
       <c r="W24" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X24" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="25.5">
       <c r="A25" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E25" s="16">
         <v>0.7</v>
@@ -2651,23 +2660,23 @@
         <v>320</v>
       </c>
       <c r="G25" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L25" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M25" s="9">
         <v>4</v>
@@ -2683,7 +2692,7 @@
         <v>576</v>
       </c>
       <c r="S25" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="20"/>
@@ -2692,25 +2701,25 @@
         <v/>
       </c>
       <c r="W25" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X25" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="25.5">
       <c r="A26" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E26" s="16">
         <v>0.7</v>
@@ -2719,23 +2728,23 @@
         <v>320</v>
       </c>
       <c r="G26" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L26" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M26" s="9">
         <v>8</v>
@@ -2751,7 +2760,7 @@
         <v>1152</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="20"/>
@@ -2760,25 +2769,25 @@
         <v/>
       </c>
       <c r="W26" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X26" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="25.5">
       <c r="A27" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E27" s="16">
         <v>0</v>
@@ -2787,23 +2796,23 @@
         <v>40</v>
       </c>
       <c r="G27" s="18">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M27" s="9">
         <v>8</v>
@@ -2819,7 +2828,7 @@
         <v>576</v>
       </c>
       <c r="S27" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="20"/>
@@ -2828,25 +2837,25 @@
         <v/>
       </c>
       <c r="W27" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X27" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="25.5">
       <c r="A28" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E28" s="16">
         <v>0.7</v>
@@ -2855,23 +2864,23 @@
         <v>320</v>
       </c>
       <c r="G28" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M28" s="9">
         <v>8</v>
@@ -2887,7 +2896,7 @@
         <v>1152</v>
       </c>
       <c r="S28" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T28" s="9"/>
       <c r="U28" s="20"/>
@@ -2896,25 +2905,25 @@
         <v/>
       </c>
       <c r="W28" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X28" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="25.5">
       <c r="A29" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E29" s="16">
         <v>0</v>
@@ -2923,23 +2932,23 @@
         <v>40</v>
       </c>
       <c r="G29" s="18">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M29" s="9">
         <v>1</v>
@@ -2955,7 +2964,7 @@
         <v>72</v>
       </c>
       <c r="S29" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T29" s="9"/>
       <c r="U29" s="20"/>
@@ -2964,25 +2973,25 @@
         <v/>
       </c>
       <c r="W29" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X29" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="25.5">
       <c r="A30" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E30" s="16">
         <v>0.7</v>
@@ -2991,23 +3000,23 @@
         <v>320</v>
       </c>
       <c r="G30" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L30" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M30" s="9">
         <v>4</v>
@@ -3023,7 +3032,7 @@
         <v>576</v>
       </c>
       <c r="S30" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T30" s="9"/>
       <c r="U30" s="20"/>
@@ -3032,25 +3041,25 @@
         <v/>
       </c>
       <c r="W30" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X30" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="25.5">
       <c r="A31" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E31" s="16">
         <v>0.7</v>
@@ -3059,23 +3068,23 @@
         <v>320</v>
       </c>
       <c r="G31" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M31" s="9">
         <v>4</v>
@@ -3091,7 +3100,7 @@
         <v>576</v>
       </c>
       <c r="S31" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T31" s="9"/>
       <c r="U31" s="20"/>
@@ -3100,25 +3109,25 @@
         <v/>
       </c>
       <c r="W31" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X31" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="25.5">
       <c r="A32" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E32" s="16">
         <v>0.7</v>
@@ -3127,23 +3136,23 @@
         <v>320</v>
       </c>
       <c r="G32" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M32" s="9">
         <v>4</v>
@@ -3159,7 +3168,7 @@
         <v>576</v>
       </c>
       <c r="S32" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T32" s="9"/>
       <c r="U32" s="20"/>
@@ -3168,25 +3177,25 @@
         <v/>
       </c>
       <c r="W32" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X32" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="25.5">
       <c r="A33" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E33" s="16">
         <v>0</v>
@@ -3195,23 +3204,23 @@
         <v>80</v>
       </c>
       <c r="G33" s="18">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M33" s="9">
         <v>1</v>
@@ -3227,7 +3236,7 @@
         <v>72</v>
       </c>
       <c r="S33" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="20"/>
@@ -3236,25 +3245,25 @@
         <v/>
       </c>
       <c r="W33" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X33" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="25.5">
       <c r="A34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E34" s="16">
         <v>0</v>
@@ -3263,23 +3272,23 @@
         <v>80</v>
       </c>
       <c r="G34" s="18">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M34" s="9">
         <v>1</v>
@@ -3295,7 +3304,7 @@
         <v>72</v>
       </c>
       <c r="S34" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="20"/>
@@ -3304,25 +3313,25 @@
         <v/>
       </c>
       <c r="W34" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X34" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="25.5">
       <c r="A35" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" s="16">
         <v>0.7</v>
@@ -3331,23 +3340,23 @@
         <v>320</v>
       </c>
       <c r="G35" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L35" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M35" s="9">
         <v>3</v>
@@ -3363,7 +3372,7 @@
         <v>432</v>
       </c>
       <c r="S35" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T35" s="9"/>
       <c r="U35" s="20"/>
@@ -3372,25 +3381,25 @@
         <v/>
       </c>
       <c r="W35" s="20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X35" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="25.5">
       <c r="A36" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E36" s="17">
         <v>0.7</v>
@@ -3398,24 +3407,24 @@
       <c r="F36" s="19">
         <v>320</v>
       </c>
-      <c r="G36" s="18">
-        <f t="shared" si="1"/>
-        <v>421</v>
+      <c r="G36" s="19">
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M36" s="14">
         <v>4</v>
@@ -3431,7 +3440,7 @@
         <v>576</v>
       </c>
       <c r="S36" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T36" s="14"/>
       <c r="U36" s="21"/>
@@ -3440,11 +3449,11 @@
         <v/>
       </c>
       <c r="W36" s="21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="X36" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3457,8 +3466,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U36"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="13.5"/>
+  <dimension ref="A1:X37"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -3471,15 +3480,18 @@
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
-    <col min="17" max="18" width="12" customWidth="1"/>
-    <col min="19" max="20" width="14" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="16" max="16" width="15.625" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="24" customWidth="1"/>
+    <col min="20" max="21" width="12" customWidth="1"/>
+    <col min="22" max="23" width="14" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="20.65">
+    <row r="1" spans="1:24" ht="20.25">
       <c r="A1" s="27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -3501,8 +3513,11 @@
       <c r="S1" s="27"/>
       <c r="T1" s="27"/>
       <c r="U1" s="27"/>
-    </row>
-    <row r="2" spans="1:21" ht="27.75">
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+    </row>
+    <row r="2" spans="1:24" ht="30">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3522,63 +3537,72 @@
         <v>6</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="P2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="R2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="W2" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="X2" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="16">
         <v>0</v>
@@ -3587,61 +3611,74 @@
         <v>80</v>
       </c>
       <c r="G3" s="18">
-        <f>ROUND(F3/0.76,0)</f>
-        <v>105</v>
+        <f t="shared" ref="G3:G37" si="0">ROUND(F3/0.8,0)</f>
+        <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="M3" s="9">
+        <v>1</v>
+      </c>
       <c r="N3" s="20">
+        <f>2*36*M3</f>
         <v>72</v>
       </c>
-      <c r="O3" s="20" t="str">
-        <f t="shared" ref="O3:O36" si="0">IF(OR(M3="",N3=""),"",M3*N3)</f>
-        <v/>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20" t="str">
-        <f t="shared" ref="S3:S36" si="1">IF(OR(Q3="",R3=""),"",Q3*R3)</f>
-        <v/>
-      </c>
-      <c r="T3" s="20" t="str">
-        <f t="shared" ref="T3:T36" si="2">IF(OR(O3="",S3=""),"",O3-S3)</f>
-        <v/>
-      </c>
-      <c r="U3" s="10" t="s">
+      <c r="O3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P3" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="25">
+        <f>4*36*P3</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="20">
+        <f>N3+Q3</f>
+        <v>72</v>
+      </c>
+      <c r="S3" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" ht="25.5">
+      <c r="T3" s="9"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20" t="str">
+        <f t="shared" ref="V3:V37" si="1">IF(OR(T3="",U3=""),"",T3*U3)</f>
+        <v/>
+      </c>
+      <c r="W3" s="20" t="str">
+        <f t="shared" ref="W3:W37" si="2">IF(OR(R3="",V3=""),"",R3-V3)</f>
+        <v/>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E4" s="16">
         <v>0</v>
@@ -3650,61 +3687,74 @@
         <v>40</v>
       </c>
       <c r="G4" s="18">
-        <f t="shared" ref="G4:G36" si="3">ROUND(F4/0.76,0)</f>
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="M4" s="9">
+        <v>2</v>
+      </c>
       <c r="N4" s="20">
-        <v>72</v>
-      </c>
-      <c r="O4" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T4" s="20" t="str">
+        <f t="shared" ref="N4:N23" si="3">2*36*M4</f>
+        <v>144</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="25">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="25">
+        <f t="shared" ref="Q4:Q23" si="4">4*36*P4</f>
+        <v>720</v>
+      </c>
+      <c r="R4" s="20">
+        <f t="shared" ref="R4:R23" si="5">N4+Q4</f>
+        <v>864</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="9"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W4" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U4" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" ht="25.5">
+      <c r="X4" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="25.5">
       <c r="A5" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" s="16">
         <v>0</v>
@@ -3713,61 +3763,74 @@
         <v>40</v>
       </c>
       <c r="G5" s="18">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+      <c r="N5" s="20">
         <f t="shared" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="20">
-        <v>72</v>
-      </c>
-      <c r="O5" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T5" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="25">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="R5" s="20">
+        <f t="shared" si="5"/>
+        <v>144</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" s="9"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W5" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U5" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="25.5">
+      <c r="X5" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="25.5">
       <c r="A6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E6" s="16">
         <v>0</v>
@@ -3776,61 +3839,74 @@
         <v>80</v>
       </c>
       <c r="G6" s="18">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" s="9">
+        <v>1</v>
+      </c>
+      <c r="N6" s="20">
         <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="H6" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="20">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T6" s="9"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W6" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X6" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="25.5">
+      <c r="A7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="20">
-        <v>72</v>
-      </c>
-      <c r="O6" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T6" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" ht="25.5">
-      <c r="A7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="E7" s="16">
         <v>0</v>
@@ -3839,61 +3915,74 @@
         <v>80</v>
       </c>
       <c r="G7" s="18">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="9">
+        <v>1</v>
+      </c>
+      <c r="N7" s="20">
         <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="H7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O7" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P7" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="20">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T7" s="9"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W7" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="25.5">
+      <c r="A8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="20">
-        <v>72</v>
-      </c>
-      <c r="O7" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T7" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U7" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="25.5">
-      <c r="A8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="E8" s="16">
         <v>0</v>
@@ -3902,61 +3991,74 @@
         <v>80</v>
       </c>
       <c r="G8" s="18">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="9">
+        <v>1</v>
+      </c>
+      <c r="N8" s="20">
         <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="20">
         <v>72</v>
       </c>
-      <c r="O8" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P8" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T8" s="20" t="str">
+      <c r="O8" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P8" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="20">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T8" s="9"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W8" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U8" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" ht="25.5">
+      <c r="X8" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="25.5">
       <c r="A9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E9" s="16">
         <v>0</v>
@@ -3965,61 +4067,74 @@
         <v>160</v>
       </c>
       <c r="G9" s="18">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="9">
+        <v>1</v>
+      </c>
+      <c r="N9" s="20">
         <f t="shared" si="3"/>
-        <v>211</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="20">
         <v>72</v>
       </c>
-      <c r="O9" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T9" s="20" t="str">
+      <c r="O9" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P9" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="20">
+        <f t="shared" si="5"/>
+        <v>72</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="9"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W9" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U9" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" ht="25.5">
+      <c r="X9" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" s="16">
         <v>0.7</v>
@@ -4028,61 +4143,74 @@
         <v>320</v>
       </c>
       <c r="G10" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="20">
-        <v>144</v>
-      </c>
-      <c r="O10" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P10" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O10" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T10" s="20" t="str">
+      <c r="P10" s="25">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="25">
+        <f t="shared" si="4"/>
+        <v>576</v>
+      </c>
+      <c r="R10" s="20">
+        <f t="shared" si="5"/>
+        <v>576</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T10" s="9"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W10" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U10" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="25.5">
+      <c r="X10" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11" s="16">
         <v>0.7</v>
@@ -4091,61 +4219,74 @@
         <v>320</v>
       </c>
       <c r="G11" s="18">
+        <f t="shared" ref="G11" si="6">ROUND(F11/0.8,0)</f>
+        <v>400</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="20">
-        <v>144</v>
-      </c>
-      <c r="O11" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P11" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O11" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T11" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U11" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="25.5">
+      <c r="P11" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="25">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="R11" s="20">
+        <f>N11+Q11</f>
+        <v>288</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T11" s="9"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20" t="str">
+        <f t="shared" ref="V11" si="7">IF(OR(T11="",U11=""),"",T11*U11)</f>
+        <v/>
+      </c>
+      <c r="W11" s="20" t="str">
+        <f t="shared" ref="W11" si="8">IF(OR(R11="",V11=""),"",R11-V11)</f>
+        <v/>
+      </c>
+      <c r="X11" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="E12" s="16">
         <v>0.7</v>
@@ -4154,61 +4295,74 @@
         <v>320</v>
       </c>
       <c r="G12" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="20">
-        <v>144</v>
-      </c>
-      <c r="O12" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P12" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O12" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T12" s="20" t="str">
+      <c r="P12" s="25">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="25">
+        <f t="shared" si="4"/>
+        <v>864</v>
+      </c>
+      <c r="R12" s="20">
+        <f t="shared" si="5"/>
+        <v>864</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T12" s="9"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W12" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U12" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" ht="25.5">
+      <c r="X12" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E13" s="16">
         <v>0.7</v>
@@ -4217,124 +4371,150 @@
         <v>320</v>
       </c>
       <c r="G13" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="20">
-        <v>144</v>
-      </c>
-      <c r="O13" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O13" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T13" s="20" t="str">
+      <c r="P13" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="25">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="R13" s="20">
+        <f t="shared" si="5"/>
+        <v>288</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T13" s="9"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W13" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U13" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" ht="25.5">
+      <c r="X13" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="25.5">
       <c r="A14" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="E14" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F14" s="18">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="G14" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20">
         <f t="shared" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="20">
-        <v>72</v>
-      </c>
-      <c r="O14" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P14" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T14" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="O14" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P14" s="25">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="25">
+        <f t="shared" si="4"/>
+        <v>432</v>
+      </c>
+      <c r="R14" s="20">
+        <f t="shared" si="5"/>
+        <v>432</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T14" s="9"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W14" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U14" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="25.5">
+      <c r="X14" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>76</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E15" s="16">
         <v>0</v>
@@ -4343,124 +4523,150 @@
         <v>40</v>
       </c>
       <c r="G15" s="18">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15" s="9">
+        <v>0</v>
+      </c>
+      <c r="N15" s="20">
         <f t="shared" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="O15" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P15" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="25">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="R15" s="20">
+        <f t="shared" si="5"/>
+        <v>288</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T15" s="9"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W15" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X15" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="25.5">
+      <c r="A16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="E16" s="16">
+        <v>0</v>
+      </c>
+      <c r="F16" s="18">
+        <v>40</v>
+      </c>
+      <c r="G16" s="18">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="J16" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="L15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="20">
-        <v>72</v>
-      </c>
-      <c r="O15" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P15" s="9" t="s">
+      <c r="K16" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="L16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T15" s="20" t="str">
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P16" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="25">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="R16" s="20">
+        <f t="shared" si="5"/>
+        <v>144</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T16" s="9"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W16" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U15" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" ht="25.5">
-      <c r="A16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="X16" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="25.5">
+      <c r="A17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="F16" s="18">
-        <v>320</v>
-      </c>
-      <c r="G16" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="20">
-        <v>144</v>
-      </c>
-      <c r="O16" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P16" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T16" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U16" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" ht="25.5">
-      <c r="A17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="E17" s="16">
         <v>0.7</v>
@@ -4469,187 +4675,226 @@
         <v>320</v>
       </c>
       <c r="G17" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0</v>
+      </c>
+      <c r="N17" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="20">
-        <v>144</v>
-      </c>
-      <c r="O17" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P17" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O17" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T17" s="20" t="str">
+      <c r="P17" s="25">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="25">
+        <f t="shared" si="4"/>
+        <v>576</v>
+      </c>
+      <c r="R17" s="20">
+        <f t="shared" si="5"/>
+        <v>576</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T17" s="9"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W17" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U17" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" ht="25.5">
+      <c r="X17" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="25.5">
       <c r="A18" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>128</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E18" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F18" s="18">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="G18" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="20">
         <f t="shared" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M18" s="9"/>
-      <c r="N18" s="20">
-        <v>72</v>
-      </c>
-      <c r="O18" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T18" s="20" t="str">
+        <v>0</v>
+      </c>
+      <c r="O18" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P18" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="25">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="R18" s="20">
+        <f t="shared" si="5"/>
+        <v>288</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T18" s="9"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W18" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U18" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" ht="25.5">
+      <c r="X18" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>129</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E19" s="16">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="18">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="G19" s="18">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0</v>
+      </c>
+      <c r="N19" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="20">
-        <v>144</v>
-      </c>
-      <c r="O19" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P19" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O19" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T19" s="20" t="str">
+      <c r="P19" s="25">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="25">
+        <f t="shared" si="4"/>
+        <v>864</v>
+      </c>
+      <c r="R19" s="20">
+        <f t="shared" si="5"/>
+        <v>864</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T19" s="9"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W19" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U19" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="25.5">
+      <c r="X19" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
       <c r="A20" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>130</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E20" s="16">
         <v>0.7</v>
@@ -4658,61 +4903,74 @@
         <v>320</v>
       </c>
       <c r="G20" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M20" s="9"/>
-      <c r="N20" s="20">
-        <v>144</v>
-      </c>
-      <c r="O20" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P20" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O20" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T20" s="20" t="str">
+      <c r="P20" s="25">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="25">
+        <f t="shared" si="4"/>
+        <v>576</v>
+      </c>
+      <c r="R20" s="20">
+        <f t="shared" si="5"/>
+        <v>576</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T20" s="9"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W20" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U20" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="25.5">
+      <c r="X20" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="25.5">
       <c r="A21" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E21" s="16">
         <v>0.7</v>
@@ -4721,61 +4979,74 @@
         <v>320</v>
       </c>
       <c r="G21" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+      <c r="N21" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="20">
+        <v>0</v>
+      </c>
+      <c r="O21" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P21" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="25">
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
-      <c r="O21" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q21" s="9"/>
-      <c r="R21" s="20"/>
-      <c r="S21" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T21" s="20" t="str">
+      <c r="R21" s="20">
+        <f t="shared" si="5"/>
+        <v>144</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T21" s="9"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W21" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U21" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="25.5">
+      <c r="X21" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
       <c r="A22" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>132</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E22" s="16">
         <v>0.7</v>
@@ -4784,124 +5055,150 @@
         <v>320</v>
       </c>
       <c r="G22" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="20">
         <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="20">
-        <v>144</v>
-      </c>
-      <c r="O22" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P22" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="O22" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T22" s="20" t="str">
+      <c r="P22" s="25">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="25">
+        <f t="shared" si="4"/>
+        <v>576</v>
+      </c>
+      <c r="R22" s="20">
+        <f t="shared" si="5"/>
+        <v>576</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T22" s="9"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W22" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U22" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
+      <c r="X22" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="25.5">
       <c r="A23" s="6" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E23" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F23" s="18">
+        <v>320</v>
+      </c>
+      <c r="G23" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0</v>
+      </c>
+      <c r="N23" s="20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="25">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="25">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="R23" s="20">
+        <f t="shared" si="5"/>
+        <v>288</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T23" s="9"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W23" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X23" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="A24" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="G23" s="18">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="20">
-        <v>72</v>
-      </c>
-      <c r="O23" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T23" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U23" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="25.5">
-      <c r="A24" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>134</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="E24" s="16">
         <v>0</v>
@@ -4910,124 +5207,130 @@
         <v>80</v>
       </c>
       <c r="G24" s="18">
-        <f t="shared" si="3"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M24" s="9"/>
       <c r="N24" s="20">
         <v>72</v>
       </c>
-      <c r="O24" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P24" s="9" t="s">
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="20" t="str">
+        <f t="shared" ref="R24:R37" si="9">IF(OR(M24="",N24=""),"",M24*N24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T24" s="9"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W24" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X24" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="25.5">
+      <c r="A25" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="16">
+        <v>0</v>
+      </c>
+      <c r="F25" s="18">
+        <v>80</v>
+      </c>
+      <c r="G25" s="18">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="L25" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T24" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U24" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="25.5">
-      <c r="A25" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="F25" s="18">
-        <v>320</v>
-      </c>
-      <c r="G25" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="20">
-        <v>144</v>
-      </c>
-      <c r="O25" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T25" s="20" t="str">
+        <v>72</v>
+      </c>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T25" s="9"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W25" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U25" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="25.5">
+      <c r="X25" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
       <c r="A26" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="E26" s="16">
         <v>0.7</v>
@@ -5036,61 +5339,64 @@
         <v>320</v>
       </c>
       <c r="G26" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M26" s="9"/>
       <c r="N26" s="20">
         <v>144</v>
       </c>
-      <c r="O26" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T26" s="20" t="str">
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T26" s="9"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W26" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U26" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="25.5">
+      <c r="X26" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="25.5">
       <c r="A27" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E27" s="16">
         <v>0.7</v>
@@ -5099,187 +5405,196 @@
         <v>320</v>
       </c>
       <c r="G27" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M27" s="9"/>
       <c r="N27" s="20">
         <v>144</v>
       </c>
-      <c r="O27" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P27" s="9" t="s">
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T27" s="9"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W27" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X27" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="A28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="16">
+        <v>0.7</v>
+      </c>
+      <c r="F28" s="18">
+        <v>320</v>
+      </c>
+      <c r="G28" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L28" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T27" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U27" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="25.5">
-      <c r="A28" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" s="16">
-        <v>0.85</v>
-      </c>
-      <c r="F28" s="18">
-        <v>160</v>
-      </c>
-      <c r="G28" s="18">
-        <f t="shared" si="3"/>
-        <v>211</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="M28" s="9"/>
       <c r="N28" s="20">
-        <v>72</v>
-      </c>
-      <c r="O28" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T28" s="20" t="str">
+        <v>144</v>
+      </c>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T28" s="9"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W28" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U28" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" ht="25.5">
+      <c r="X28" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24">
       <c r="A29" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="E29" s="16">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F29" s="18">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="G29" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>200</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>52</v>
+        <v>142</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>67</v>
+        <v>145</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M29" s="9"/>
       <c r="N29" s="20">
-        <v>144</v>
-      </c>
-      <c r="O29" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T29" s="20" t="str">
+        <v>72</v>
+      </c>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T29" s="9"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W29" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U29" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="25.5">
+      <c r="X29" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24">
       <c r="A30" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E30" s="16">
         <v>0.7</v>
@@ -5288,431 +5603,519 @@
         <v>320</v>
       </c>
       <c r="G30" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M30" s="9"/>
       <c r="N30" s="20">
         <v>144</v>
       </c>
-      <c r="O30" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P30" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T30" s="20" t="str">
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T30" s="9"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W30" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U30" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="25.5">
+      <c r="X30" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="25.5">
       <c r="A31" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>92</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E31" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F31" s="18">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="G31" s="18">
-        <f t="shared" si="3"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M31" s="9"/>
       <c r="N31" s="20">
-        <v>72</v>
-      </c>
-      <c r="O31" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T31" s="20" t="str">
+        <v>144</v>
+      </c>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T31" s="9"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W31" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U31" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="25.5">
+      <c r="X31" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="25.5">
       <c r="A32" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E32" s="16">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F32" s="18">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="G32" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
+        <f>ROUND(F32/0.8,0)</f>
+        <v>100</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M32" s="9"/>
       <c r="N32" s="20">
-        <v>144</v>
-      </c>
-      <c r="O32" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P32" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T32" s="20" t="str">
+        <v>72</v>
+      </c>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S32" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T32" s="9"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W32" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U32" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="25.5">
+      <c r="X32" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24">
       <c r="A33" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>94</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="E33" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F33" s="18">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="G33" s="18">
-        <f t="shared" si="3"/>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>400</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M33" s="9"/>
       <c r="N33" s="20">
-        <v>72</v>
-      </c>
-      <c r="O33" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T33" s="20" t="str">
+        <v>144</v>
+      </c>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T33" s="9"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W33" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U33" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="25.5">
+      <c r="X33" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="25.5">
       <c r="A34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>95</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E34" s="16">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F34" s="18">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="G34" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M34" s="9"/>
       <c r="N34" s="20">
-        <v>144</v>
-      </c>
-      <c r="O34" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P34" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S34" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T34" s="9"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W34" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X34" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24">
+      <c r="A35" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="16">
+        <v>0.7</v>
+      </c>
+      <c r="F35" s="18">
+        <v>320</v>
+      </c>
+      <c r="G35" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L35" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="Q34" s="9"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T34" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="U34" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" ht="25.5">
-      <c r="A35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E35" s="16">
-        <v>0</v>
-      </c>
-      <c r="F35" s="18">
-        <v>80</v>
-      </c>
-      <c r="G35" s="18">
-        <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="M35" s="9"/>
       <c r="N35" s="20">
+        <v>144</v>
+      </c>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S35" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T35" s="9"/>
+      <c r="U35" s="20"/>
+      <c r="V35" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W35" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X35" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="25.5">
+      <c r="A36" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="16">
+        <v>0</v>
+      </c>
+      <c r="F36" s="18">
+        <v>80</v>
+      </c>
+      <c r="G36" s="18">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M36" s="9"/>
+      <c r="N36" s="20">
         <v>72</v>
       </c>
-      <c r="O35" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T35" s="20" t="str">
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="20" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S36" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="T36" s="9"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W36" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U35" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" ht="25.5">
-      <c r="A36" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="X36" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" ht="25.5">
+      <c r="A37" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="17">
+      <c r="D37" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="17">
         <v>0.7</v>
       </c>
-      <c r="F36" s="19">
+      <c r="F37" s="19">
         <v>320</v>
       </c>
-      <c r="G36" s="18">
-        <f t="shared" si="3"/>
-        <v>421</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I36" s="13" t="s">
+      <c r="G37" s="19">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="H37" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="I37" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="K36" s="13" t="s">
+      <c r="J37" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="L36" s="14" t="s">
+      <c r="K37" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="M36" s="14"/>
-      <c r="N36" s="21">
+      <c r="L37" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M37" s="14"/>
+      <c r="N37" s="21">
         <v>144</v>
       </c>
-      <c r="O36" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P36" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="21"/>
-      <c r="S36" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="T36" s="21" t="str">
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="21" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S37" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="T37" s="14"/>
+      <c r="U37" s="21"/>
+      <c r="V37" s="21" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W37" s="21" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="U36" s="15" t="s">
-        <v>31</v>
+      <c r="X37" s="15" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5720,7 +6123,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.8125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -5728,9 +6131,9 @@
     <col min="6" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.65">
+    <row r="1" spans="1:8" ht="20.25">
       <c r="A1" s="28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -5740,35 +6143,35 @@
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
     </row>
-    <row r="2" spans="1:8" ht="27.75">
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="27">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.5">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="22">
         <v>0.7</v>
@@ -5781,21 +6184,21 @@
         <v>400</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="27">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.5">
       <c r="A4" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B4" s="22">
         <v>0.7</v>
@@ -5808,21 +6211,21 @@
         <v>400</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B5" s="22">
         <v>0.7</v>
@@ -5835,21 +6238,21 @@
         <v>400</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="22">
         <v>0</v>
@@ -5862,21 +6265,21 @@
         <v>50</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="22">
         <v>0</v>
@@ -5889,21 +6292,21 @@
         <v>100</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="22">
         <v>0</v>
@@ -5916,21 +6319,21 @@
         <v>100</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="22">
         <v>0</v>
@@ -5943,21 +6346,21 @@
         <v>100</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="27">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.5">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B10" s="22">
         <v>0</v>
@@ -5970,21 +6373,21 @@
         <v>200</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B11" s="22">
         <v>0.85</v>
@@ -5997,21 +6400,21 @@
         <v>200</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B12" s="22">
         <v>0.85</v>
@@ -6024,16 +6427,16 @@
         <v>300</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Building A B Lighting New.xlsx
+++ b/excel/Building A B Lighting New.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lsen906\Documents\Alpha_Design_17\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pacopoon/Downloads/Alpha_Design_17/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF100CD-F807-4868-89E7-1A2A637BF8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F837A4F-C3CE-C444-90DA-145521EAE380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Building A" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="192">
   <si>
     <t>Building A — Lighting Place Schedule</t>
   </si>
@@ -127,9 +127,6 @@
     <t>Measure on stair tread/floor path</t>
   </si>
   <si>
-    <t>Batten 2 × 36W</t>
-  </si>
-  <si>
     <t>LED batten / linear</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>Use dimming if presentation mode is required</t>
   </si>
   <si>
-    <t>Troffer 4 × 36W</t>
-  </si>
-  <si>
     <t>LED low-glare panel</t>
   </si>
   <si>
@@ -611,6 +605,12 @@
   </si>
   <si>
     <t>Existing W (2)</t>
+  </si>
+  <si>
+    <t>Philips 2x36W</t>
+  </si>
+  <si>
+    <t>Philips 4x36W SLB</t>
   </si>
 </sst>
 </file>
@@ -682,13 +682,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FF000000"/>
+        <fgColor rgb="FFF8FBFD"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FBFD"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -768,7 +768,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -839,11 +839,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -852,108 +855,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -986,6 +902,13 @@
       <fill>
         <patternFill>
           <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1157,7 +1080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y36"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -1170,39 +1093,39 @@
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="8.375" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" customWidth="1"/>
     <col min="17" max="19" width="12" customWidth="1"/>
     <col min="20" max="21" width="14" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.25">
-      <c r="A1" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-    </row>
-    <row r="2" spans="1:25" ht="45">
+    <row r="1" spans="1:25" ht="21">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+    </row>
+    <row r="2" spans="1:25" ht="48">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1237,7 +1160,7 @@
         <v>11</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>13</v>
@@ -1246,7 +1169,7 @@
         <v>14</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>13</v>
@@ -1257,8 +1180,8 @@
       <c r="R2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="29" t="s">
-        <v>187</v>
+      <c r="S2" s="26" t="s">
+        <v>185</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>16</v>
@@ -1279,7 +1202,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="25.5">
+    <row r="3" spans="1:25" ht="29">
       <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
@@ -1315,7 +1238,7 @@
         <v>29</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M3" s="9">
         <v>1</v>
@@ -1323,18 +1246,18 @@
       <c r="N3" s="20">
         <v>72</v>
       </c>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
       <c r="R3" s="20">
         <f>IF(OR(M3="",N3=""),"",M3*N3)</f>
         <v>72</v>
       </c>
-      <c r="S3" s="30" t="s">
-        <v>189</v>
+      <c r="S3" s="27" t="s">
+        <v>187</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U3" s="9"/>
       <c r="V3" s="20"/>
@@ -1347,21 +1270,21 @@
         <v/>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="29">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="E4" s="16">
         <v>0</v>
@@ -1377,16 +1300,16 @@
         <v>26</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L4" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M4" s="9">
         <v>2</v>
@@ -1394,13 +1317,13 @@
       <c r="N4" s="20">
         <v>72</v>
       </c>
-      <c r="O4" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="25">
+      <c r="O4" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" s="24">
         <v>5</v>
       </c>
-      <c r="Q4" s="25">
+      <c r="Q4" s="24">
         <f>4*36</f>
         <v>144</v>
       </c>
@@ -1408,11 +1331,11 @@
         <f>IF(OR(M4="",N4=""),"",M4*N4+Q4)</f>
         <v>288</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="27">
         <v>503</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U4" s="9"/>
       <c r="V4" s="20"/>
@@ -1425,21 +1348,21 @@
         <v/>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="29">
       <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="E5" s="16">
         <v>0</v>
@@ -1452,19 +1375,19 @@
         <v>100</v>
       </c>
       <c r="H5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L5" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M5" s="9">
         <v>1</v>
@@ -1472,18 +1395,18 @@
       <c r="N5" s="20">
         <v>72</v>
       </c>
-      <c r="O5" s="26"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
       <c r="R5" s="20">
         <f t="shared" ref="R5:R35" si="2">IF(OR(M5="",N5=""),"",M5*N5)</f>
         <v>72</v>
       </c>
-      <c r="S5" s="30">
+      <c r="S5" s="27">
         <v>209</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U5" s="9"/>
       <c r="V5" s="20"/>
@@ -1496,21 +1419,21 @@
         <v/>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="29">
       <c r="A6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="E6" s="16">
         <v>0</v>
@@ -1523,19 +1446,19 @@
         <v>100</v>
       </c>
       <c r="H6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L6" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M6" s="9">
         <v>1</v>
@@ -1543,18 +1466,18 @@
       <c r="N6" s="20">
         <v>72</v>
       </c>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
       <c r="R6" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S6" s="30">
+      <c r="S6" s="27">
         <v>209</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U6" s="9"/>
       <c r="V6" s="20"/>
@@ -1567,21 +1490,21 @@
         <v/>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="29">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="E7" s="16">
         <v>0</v>
@@ -1594,19 +1517,19 @@
         <v>100</v>
       </c>
       <c r="H7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="J7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L7" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M7" s="9">
         <v>1</v>
@@ -1614,18 +1537,18 @@
       <c r="N7" s="20">
         <v>72</v>
       </c>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
       <c r="R7" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S7" s="30">
+      <c r="S7" s="27">
         <v>183</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U7" s="9"/>
       <c r="V7" s="20"/>
@@ -1638,21 +1561,21 @@
         <v/>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="29">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E8" s="16">
         <v>0.7</v>
@@ -1665,19 +1588,19 @@
         <v>400</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>57</v>
+      <c r="L8" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M8" s="9">
         <v>2</v>
@@ -1685,18 +1608,18 @@
       <c r="N8" s="20">
         <v>144</v>
       </c>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
       <c r="R8" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S8" s="30">
+      <c r="S8" s="27">
         <v>625</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U8" s="9"/>
       <c r="V8" s="20"/>
@@ -1709,21 +1632,21 @@
         <v/>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="29">
       <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E9" s="16">
         <v>0.7</v>
@@ -1736,19 +1659,19 @@
         <v>400</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>57</v>
+      <c r="L9" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M9" s="9">
         <v>2</v>
@@ -1756,18 +1679,18 @@
       <c r="N9" s="20">
         <v>144</v>
       </c>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
       <c r="R9" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S9" s="30">
+      <c r="S9" s="27">
         <v>644</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U9" s="9"/>
       <c r="V9" s="20"/>
@@ -1780,21 +1703,21 @@
         <v/>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="29">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="E10" s="16">
         <v>0</v>
@@ -1810,16 +1733,16 @@
         <v>26</v>
       </c>
       <c r="I10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L10" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M10" s="9">
         <v>4</v>
@@ -1827,13 +1750,13 @@
       <c r="N10" s="20">
         <v>72</v>
       </c>
-      <c r="O10" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P10" s="25">
+      <c r="O10" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="24">
         <v>4</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q10" s="24">
         <f>4*36</f>
         <v>144</v>
       </c>
@@ -1841,11 +1764,11 @@
         <f>IF(OR(M10="",N10=""),"",M10*N10+Q10)</f>
         <v>432</v>
       </c>
-      <c r="S10" s="30">
+      <c r="S10" s="27">
         <v>373</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U10" s="9"/>
       <c r="V10" s="20"/>
@@ -1858,21 +1781,21 @@
         <v/>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="29">
       <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="E11" s="16">
         <v>0.7</v>
@@ -1885,19 +1808,19 @@
         <v>400</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>57</v>
+      <c r="L11" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M11" s="9">
         <v>2</v>
@@ -1905,18 +1828,18 @@
       <c r="N11" s="20">
         <v>144</v>
       </c>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
       <c r="R11" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S11" s="30">
+      <c r="S11" s="27">
         <v>615</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="V11" s="20"/>
       <c r="W11" s="20" t="str">
@@ -1928,21 +1851,21 @@
         <v/>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="29">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="E12" s="16">
         <v>0.7</v>
@@ -1955,19 +1878,19 @@
         <v>400</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>57</v>
+      <c r="L12" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M12" s="9">
         <v>4</v>
@@ -1975,18 +1898,18 @@
       <c r="N12" s="20">
         <v>144</v>
       </c>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
       <c r="R12" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S12" s="30">
+      <c r="S12" s="27">
         <v>836</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U12" s="9"/>
       <c r="V12" s="20"/>
@@ -1999,21 +1922,21 @@
         <v>#REF!</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="29">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="E13" s="16">
         <v>0.7</v>
@@ -2026,19 +1949,19 @@
         <v>400</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>57</v>
+      <c r="L13" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M13" s="9">
         <v>4</v>
@@ -2046,18 +1969,18 @@
       <c r="N13" s="20">
         <v>144</v>
       </c>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
       <c r="R13" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S13" s="30">
+      <c r="S13" s="27">
         <v>743</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U13" s="9"/>
       <c r="V13" s="20"/>
@@ -2070,21 +1993,21 @@
         <v/>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="29">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E14" s="16">
         <v>0.7</v>
@@ -2097,19 +2020,19 @@
         <v>400</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I14" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>57</v>
+      <c r="L14" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M14" s="9">
         <v>6</v>
@@ -2117,18 +2040,18 @@
       <c r="N14" s="20">
         <v>144</v>
       </c>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
       <c r="R14" s="20">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="S14" s="30">
+      <c r="S14" s="27">
         <v>1088</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U14" s="9"/>
       <c r="V14" s="20"/>
@@ -2141,21 +2064,21 @@
         <v/>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="29">
       <c r="A15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E15" s="16">
         <v>0.7</v>
@@ -2168,19 +2091,19 @@
         <v>400</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I15" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>57</v>
+      <c r="L15" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M15" s="9">
         <v>3</v>
@@ -2188,18 +2111,18 @@
       <c r="N15" s="20">
         <v>144</v>
       </c>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
       <c r="R15" s="20">
         <f t="shared" si="2"/>
         <v>432</v>
       </c>
-      <c r="S15" s="30">
+      <c r="S15" s="27">
         <v>743</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U15" s="9"/>
       <c r="V15" s="20"/>
@@ -2212,21 +2135,21 @@
         <v/>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="29">
       <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="E16" s="16">
         <v>0.7</v>
@@ -2239,19 +2162,19 @@
         <v>200</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="J16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>57</v>
+      <c r="L16" s="25" t="s">
+        <v>191</v>
       </c>
       <c r="M16" s="9">
         <v>3</v>
@@ -2259,18 +2182,18 @@
       <c r="N16" s="20">
         <v>144</v>
       </c>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
       <c r="R16" s="20">
         <f t="shared" si="2"/>
         <v>432</v>
       </c>
-      <c r="S16" s="30">
+      <c r="S16" s="27">
         <v>954</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U16" s="9"/>
       <c r="V16" s="20"/>
@@ -2283,15 +2206,15 @@
         <v/>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="29">
       <c r="A17" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>24</v>
@@ -2322,7 +2245,7 @@
         <v>29</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M17" s="9">
         <v>1</v>
@@ -2330,18 +2253,18 @@
       <c r="N17" s="20">
         <v>72</v>
       </c>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
       <c r="R17" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S17" s="30">
+      <c r="S17" s="27">
         <v>150</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U17" s="9"/>
       <c r="V17" s="20"/>
@@ -2354,21 +2277,21 @@
         <v/>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="29">
       <c r="A18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E18" s="16">
         <v>0</v>
@@ -2384,16 +2307,16 @@
         <v>26</v>
       </c>
       <c r="I18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L18" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M18" s="9">
         <v>4</v>
@@ -2401,18 +2324,18 @@
       <c r="N18" s="20">
         <v>72</v>
       </c>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
       <c r="R18" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S18" s="30">
+      <c r="S18" s="27">
         <v>140</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="20"/>
@@ -2425,21 +2348,21 @@
         <v/>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="29">
       <c r="A19" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E19" s="16">
         <v>0.7</v>
@@ -2452,19 +2375,19 @@
         <v>400</v>
       </c>
       <c r="H19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="J19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="L19" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M19" s="9">
         <v>2</v>
@@ -2472,18 +2395,18 @@
       <c r="N19" s="20">
         <v>144</v>
       </c>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
       <c r="R19" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S19" s="30">
+      <c r="S19" s="27">
         <v>331</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U19" s="9"/>
       <c r="V19" s="20"/>
@@ -2496,21 +2419,21 @@
         <v/>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="29">
       <c r="A20" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="E20" s="16">
         <v>0.7</v>
@@ -2523,19 +2446,19 @@
         <v>400</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="L20" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M20" s="9">
         <v>7</v>
@@ -2543,18 +2466,18 @@
       <c r="N20" s="20">
         <v>144</v>
       </c>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
       <c r="R20" s="20">
         <f t="shared" si="2"/>
         <v>1008</v>
       </c>
-      <c r="S20" s="30">
+      <c r="S20" s="27">
         <v>470</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U20" s="9"/>
       <c r="V20" s="20"/>
@@ -2567,21 +2490,21 @@
         <v/>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="29">
       <c r="A21" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="E21" s="16">
         <v>0</v>
@@ -2597,16 +2520,16 @@
         <v>26</v>
       </c>
       <c r="I21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L21" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M21" s="9">
         <v>1</v>
@@ -2614,18 +2537,18 @@
       <c r="N21" s="20">
         <v>72</v>
       </c>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
       <c r="R21" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="27">
         <v>181</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U21" s="9"/>
       <c r="V21" s="20"/>
@@ -2638,21 +2561,21 @@
         <v/>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="29">
       <c r="A22" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="E22" s="16">
         <v>0</v>
@@ -2665,19 +2588,19 @@
         <v>100</v>
       </c>
       <c r="H22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L22" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M22" s="9">
         <v>2</v>
@@ -2685,18 +2608,18 @@
       <c r="N22" s="20">
         <v>72</v>
       </c>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
       <c r="R22" s="20">
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="27">
         <v>269</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U22" s="9"/>
       <c r="V22" s="20"/>
@@ -2709,21 +2632,21 @@
         <v/>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="29">
       <c r="A23" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E23" s="16">
         <v>0.7</v>
@@ -2736,19 +2659,19 @@
         <v>400</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I23" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J23" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L23" s="24" t="s">
-        <v>30</v>
+      <c r="L23" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M23" s="9">
         <v>6</v>
@@ -2756,18 +2679,18 @@
       <c r="N23" s="20">
         <v>144</v>
       </c>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
       <c r="R23" s="20">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="S23" s="30">
+      <c r="S23" s="27">
         <v>516</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U23" s="9"/>
       <c r="V23" s="20"/>
@@ -2780,21 +2703,21 @@
         <v/>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="29">
       <c r="A24" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E24" s="16">
         <v>0.7</v>
@@ -2807,19 +2730,19 @@
         <v>400</v>
       </c>
       <c r="H24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="J24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L24" s="24" t="s">
-        <v>30</v>
+      <c r="L24" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M24" s="9">
         <v>4</v>
@@ -2827,18 +2750,18 @@
       <c r="N24" s="20">
         <v>144</v>
       </c>
-      <c r="O24" s="25"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="24"/>
       <c r="R24" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="27">
         <v>458</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U24" s="9"/>
       <c r="V24" s="20"/>
@@ -2851,21 +2774,21 @@
         <v/>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="29">
       <c r="A25" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E25" s="16">
         <v>0.7</v>
@@ -2878,19 +2801,19 @@
         <v>400</v>
       </c>
       <c r="H25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="J25" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="K25" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L25" s="24" t="s">
-        <v>30</v>
+      <c r="L25" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M25" s="9">
         <v>4</v>
@@ -2898,18 +2821,18 @@
       <c r="N25" s="20">
         <v>144</v>
       </c>
-      <c r="O25" s="25"/>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="25"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
       <c r="R25" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25" s="27">
         <v>422</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U25" s="9"/>
       <c r="V25" s="20"/>
@@ -2922,21 +2845,21 @@
         <v/>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="29">
       <c r="A26" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E26" s="16">
         <v>0.7</v>
@@ -2949,19 +2872,19 @@
         <v>400</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I26" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J26" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L26" s="24" t="s">
-        <v>30</v>
+      <c r="L26" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M26" s="9">
         <v>8</v>
@@ -2969,18 +2892,18 @@
       <c r="N26" s="20">
         <v>144</v>
       </c>
-      <c r="O26" s="25"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
       <c r="R26" s="20">
         <f t="shared" si="2"/>
         <v>1152</v>
       </c>
-      <c r="S26" s="30">
+      <c r="S26" s="27">
         <v>455</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U26" s="9"/>
       <c r="V26" s="20"/>
@@ -2993,21 +2916,21 @@
         <v/>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="29">
       <c r="A27" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E27" s="16">
         <v>0</v>
@@ -3023,16 +2946,16 @@
         <v>26</v>
       </c>
       <c r="I27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K27" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L27" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M27" s="9">
         <v>8</v>
@@ -3040,18 +2963,18 @@
       <c r="N27" s="20">
         <v>72</v>
       </c>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
       <c r="R27" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="27">
         <v>133</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U27" s="9"/>
       <c r="V27" s="20"/>
@@ -3064,21 +2987,21 @@
         <v/>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="29">
       <c r="A28" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="E28" s="16">
         <v>0.7</v>
@@ -3091,19 +3014,19 @@
         <v>400</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="J28" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="K28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K28" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L28" s="24" t="s">
-        <v>30</v>
+      <c r="L28" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M28" s="9">
         <v>8</v>
@@ -3111,18 +3034,18 @@
       <c r="N28" s="20">
         <v>144</v>
       </c>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
       <c r="R28" s="20">
         <f t="shared" si="2"/>
         <v>1152</v>
       </c>
-      <c r="S28" s="30">
+      <c r="S28" s="27">
         <v>435</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U28" s="9"/>
       <c r="V28" s="20"/>
@@ -3135,21 +3058,21 @@
         <v/>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="29">
       <c r="A29" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E29" s="16">
         <v>0</v>
@@ -3165,16 +3088,16 @@
         <v>26</v>
       </c>
       <c r="I29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="K29" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L29" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M29" s="9">
         <v>1</v>
@@ -3182,18 +3105,18 @@
       <c r="N29" s="20">
         <v>72</v>
       </c>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
       <c r="R29" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S29" s="30">
+      <c r="S29" s="27">
         <v>118</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U29" s="9"/>
       <c r="V29" s="20"/>
@@ -3206,21 +3129,21 @@
         <v/>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="29">
       <c r="A30" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E30" s="16">
         <v>0.7</v>
@@ -3233,19 +3156,19 @@
         <v>400</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I30" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K30" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J30" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L30" s="24" t="s">
-        <v>30</v>
+      <c r="L30" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M30" s="9">
         <v>4</v>
@@ -3253,18 +3176,18 @@
       <c r="N30" s="20">
         <v>144</v>
       </c>
-      <c r="O30" s="25"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="25"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
       <c r="R30" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S30" s="30">
+      <c r="S30" s="27">
         <v>416</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U30" s="9"/>
       <c r="V30" s="20"/>
@@ -3277,21 +3200,21 @@
         <v/>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="29">
       <c r="A31" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E31" s="16">
         <v>0.7</v>
@@ -3304,19 +3227,19 @@
         <v>400</v>
       </c>
       <c r="H31" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="J31" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L31" s="24" t="s">
-        <v>30</v>
+      <c r="L31" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M31" s="9">
         <v>4</v>
@@ -3324,18 +3247,18 @@
       <c r="N31" s="20">
         <v>144</v>
       </c>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
       <c r="R31" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S31" s="30">
+      <c r="S31" s="27">
         <v>419</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U31" s="9"/>
       <c r="V31" s="20"/>
@@ -3348,21 +3271,21 @@
         <v/>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="29">
       <c r="A32" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E32" s="16">
         <v>0.7</v>
@@ -3375,19 +3298,19 @@
         <v>400</v>
       </c>
       <c r="H32" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I32" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="J32" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="K32" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K32" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L32" s="24" t="s">
-        <v>30</v>
+      <c r="L32" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M32" s="9">
         <v>4</v>
@@ -3395,18 +3318,18 @@
       <c r="N32" s="20">
         <v>144</v>
       </c>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
       <c r="R32" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S32" s="30">
+      <c r="S32" s="27">
         <v>400</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U32" s="9"/>
       <c r="V32" s="20"/>
@@ -3419,21 +3342,21 @@
         <v/>
       </c>
       <c r="Y32" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="29">
       <c r="A33" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="E33" s="16">
         <v>0</v>
@@ -3446,19 +3369,19 @@
         <v>100</v>
       </c>
       <c r="H33" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="J33" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L33" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M33" s="9">
         <v>1</v>
@@ -3466,18 +3389,18 @@
       <c r="N33" s="20">
         <v>72</v>
       </c>
-      <c r="O33" s="25"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
       <c r="R33" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S33" s="30">
+      <c r="S33" s="27">
         <v>140</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U33" s="9"/>
       <c r="V33" s="20"/>
@@ -3490,21 +3413,21 @@
         <v/>
       </c>
       <c r="Y33" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="29">
       <c r="A34" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="E34" s="16">
         <v>0</v>
@@ -3517,19 +3440,19 @@
         <v>100</v>
       </c>
       <c r="H34" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I34" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="J34" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="K34" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K34" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L34" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M34" s="9">
         <v>1</v>
@@ -3537,18 +3460,18 @@
       <c r="N34" s="20">
         <v>72</v>
       </c>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24"/>
       <c r="R34" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S34" s="30">
+      <c r="S34" s="27">
         <v>140</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U34" s="9"/>
       <c r="V34" s="20"/>
@@ -3561,21 +3484,21 @@
         <v/>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" ht="29">
       <c r="A35" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E35" s="16">
         <v>0.7</v>
@@ -3588,19 +3511,19 @@
         <v>400</v>
       </c>
       <c r="H35" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I35" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="J35" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="K35" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K35" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L35" s="24" t="s">
-        <v>30</v>
+      <c r="L35" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M35" s="9">
         <v>3</v>
@@ -3608,18 +3531,18 @@
       <c r="N35" s="20">
         <v>144</v>
       </c>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
       <c r="R35" s="20">
         <f t="shared" si="2"/>
         <v>432</v>
       </c>
-      <c r="S35" s="30">
+      <c r="S35" s="27">
         <v>405</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U35" s="9"/>
       <c r="V35" s="20"/>
@@ -3632,21 +3555,21 @@
         <v/>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="29">
       <c r="A36" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E36" s="17">
         <v>0.7</v>
@@ -3659,19 +3582,19 @@
         <v>400</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I36" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K36" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="J36" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="L36" s="24" t="s">
-        <v>30</v>
+      <c r="L36" s="9" t="s">
+        <v>190</v>
       </c>
       <c r="M36" s="14">
         <v>4</v>
@@ -3679,18 +3602,18 @@
       <c r="N36" s="21">
         <v>144</v>
       </c>
-      <c r="O36" s="25"/>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="24"/>
       <c r="R36" s="21">
         <f>IF(OR(M36="",N36=""),"",M36*N36)</f>
         <v>576</v>
       </c>
-      <c r="S36" s="30">
+      <c r="S36" s="27">
         <v>392</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U36" s="14"/>
       <c r="V36" s="21"/>
@@ -3703,7 +3626,7 @@
         <v/>
       </c>
       <c r="Y36" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3711,10 +3634,10 @@
     <mergeCell ref="A1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="S4:S36">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$S4&lt;$F4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$S4&gt;=$F4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3725,8 +3648,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y37"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <dimension ref="A1:Y44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -3739,7 +3662,7 @@
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="15.625" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
     <col min="18" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="24" customWidth="1"/>
@@ -3748,36 +3671,36 @@
     <col min="25" max="25" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.25">
-      <c r="A1" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-    </row>
-    <row r="2" spans="1:25" ht="45">
+    <row r="1" spans="1:25" ht="21">
+      <c r="A1" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+    </row>
+    <row r="2" spans="1:25" ht="48">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3818,22 +3741,22 @@
         <v>13</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="29" t="s">
-        <v>187</v>
+      <c r="S2" s="26" t="s">
+        <v>185</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>16</v>
@@ -3854,7 +3777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="25.5">
+    <row r="3" spans="1:25" ht="29">
       <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
@@ -3874,7 +3797,7 @@
         <v>80</v>
       </c>
       <c r="G3" s="18">
-        <f t="shared" ref="G3:G37" si="0">ROUND(F3/0.8,0)</f>
+        <f t="shared" ref="G3:G24" si="0">ROUND(F3/0.8,0)</f>
         <v>100</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -3890,7 +3813,7 @@
         <v>29</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M3" s="9">
         <v>1</v>
@@ -3899,13 +3822,13 @@
         <f>2*36*M3</f>
         <v>72</v>
       </c>
-      <c r="O3" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P3" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="25">
+      <c r="O3" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P3" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="24">
         <f>4*36*P3</f>
         <v>0</v>
       </c>
@@ -3913,38 +3836,38 @@
         <f>N3+Q3</f>
         <v>72</v>
       </c>
-      <c r="S3" s="30" t="s">
-        <v>188</v>
+      <c r="S3" s="27" t="s">
+        <v>186</v>
       </c>
       <c r="T3" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U3" s="9"/>
       <c r="V3" s="20"/>
       <c r="W3" s="20" t="str">
-        <f t="shared" ref="W3:W37" si="1">IF(OR(U3="",V3=""),"",U3*V3)</f>
+        <f t="shared" ref="W3:W24" si="1">IF(OR(U3="",V3=""),"",U3*V3)</f>
         <v/>
       </c>
       <c r="X3" s="20" t="str">
-        <f t="shared" ref="X3:X37" si="2">IF(OR(R3="",W3=""),"",R3-W3)</f>
+        <f t="shared" ref="X3:X24" si="2">IF(OR(R3="",W3=""),"",R3-W3)</f>
         <v/>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="29">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E4" s="16">
         <v>0</v>
@@ -3960,16 +3883,16 @@
         <v>26</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L4" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M4" s="9">
         <v>2</v>
@@ -3978,25 +3901,25 @@
         <f t="shared" ref="N4:N23" si="3">2*36*M4</f>
         <v>144</v>
       </c>
-      <c r="O4" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="25">
+      <c r="O4" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" s="24">
         <v>5</v>
       </c>
-      <c r="Q4" s="25">
-        <f t="shared" ref="Q4:Q23" si="4">4*36*P4</f>
+      <c r="Q4" s="24">
+        <f t="shared" ref="Q4:Q24" si="4">4*36*P4</f>
         <v>720</v>
       </c>
       <c r="R4" s="20">
         <f t="shared" ref="R4:R23" si="5">N4+Q4</f>
         <v>864</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="27">
         <v>380</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U4" s="9"/>
       <c r="V4" s="20"/>
@@ -4009,21 +3932,21 @@
         <v/>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="29">
       <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" s="16">
         <v>0</v>
@@ -4036,19 +3959,19 @@
         <v>50</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I5" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>112</v>
-      </c>
       <c r="L5" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M5" s="9">
         <v>0</v>
@@ -4057,13 +3980,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O5" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P5" s="25">
+      <c r="O5" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P5" s="24">
         <v>1</v>
       </c>
-      <c r="Q5" s="25">
+      <c r="Q5" s="24">
         <f t="shared" si="4"/>
         <v>144</v>
       </c>
@@ -4071,11 +3994,11 @@
         <f t="shared" si="5"/>
         <v>144</v>
       </c>
-      <c r="S5" s="30">
+      <c r="S5" s="27">
         <v>325</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U5" s="9"/>
       <c r="V5" s="20"/>
@@ -4088,21 +4011,21 @@
         <v/>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="29">
       <c r="A6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E6" s="16">
         <v>0</v>
@@ -4115,19 +4038,19 @@
         <v>100</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>117</v>
-      </c>
       <c r="L6" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M6" s="9">
         <v>1</v>
@@ -4136,13 +4059,13 @@
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O6" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="25">
+      <c r="O6" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P6" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4150,11 +4073,11 @@
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S6" s="30">
+      <c r="S6" s="27">
         <v>205</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U6" s="9"/>
       <c r="V6" s="20"/>
@@ -4167,21 +4090,21 @@
         <v/>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="29">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="E7" s="16">
         <v>0</v>
@@ -4194,19 +4117,19 @@
         <v>100</v>
       </c>
       <c r="H7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="J7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L7" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M7" s="9">
         <v>1</v>
@@ -4215,13 +4138,13 @@
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O7" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P7" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="25">
+      <c r="O7" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P7" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4229,11 +4152,11 @@
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S7" s="30">
+      <c r="S7" s="27">
         <v>201</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U7" s="9"/>
       <c r="V7" s="20"/>
@@ -4246,21 +4169,21 @@
         <v/>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="29">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="E8" s="16">
         <v>0</v>
@@ -4273,19 +4196,19 @@
         <v>100</v>
       </c>
       <c r="H8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L8" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M8" s="9">
         <v>1</v>
@@ -4294,13 +4217,13 @@
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O8" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P8" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="25">
+      <c r="O8" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P8" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4308,11 +4231,11 @@
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S8" s="30">
+      <c r="S8" s="27">
         <v>186</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U8" s="9"/>
       <c r="V8" s="20"/>
@@ -4325,21 +4248,21 @@
         <v/>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="29">
       <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E9" s="16">
         <v>0</v>
@@ -4352,19 +4275,19 @@
         <v>200</v>
       </c>
       <c r="H9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="L9" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M9" s="9">
         <v>1</v>
@@ -4373,13 +4296,13 @@
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O9" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P9" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="25">
+      <c r="O9" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P9" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -4387,11 +4310,11 @@
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S9" s="30">
+      <c r="S9" s="27">
         <v>187</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U9" s="9"/>
       <c r="V9" s="20"/>
@@ -4404,21 +4327,21 @@
         <v/>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="29">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10" s="16">
         <v>0.7</v>
@@ -4431,19 +4354,19 @@
         <v>400</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I10" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="L10" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M10" s="9">
         <v>0</v>
@@ -4452,13 +4375,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O10" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P10" s="25">
+      <c r="O10" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P10" s="24">
         <v>4</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q10" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
@@ -4466,11 +4389,11 @@
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S10" s="30">
+      <c r="S10" s="27">
         <v>753</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U10" s="9"/>
       <c r="V10" s="20"/>
@@ -4483,21 +4406,21 @@
         <v/>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="29">
       <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E11" s="16">
         <v>0.7</v>
@@ -4510,19 +4433,19 @@
         <v>400</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="L11" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M11" s="9">
         <v>0</v>
@@ -4531,13 +4454,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O11" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P11" s="25">
+      <c r="O11" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P11" s="24">
         <v>2</v>
       </c>
-      <c r="Q11" s="25">
+      <c r="Q11" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
@@ -4545,11 +4468,11 @@
         <f>N11+Q11</f>
         <v>288</v>
       </c>
-      <c r="S11" s="30">
+      <c r="S11" s="27">
         <v>801</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U11" s="9"/>
       <c r="V11" s="20"/>
@@ -4562,21 +4485,21 @@
         <v/>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="29">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="E12" s="16">
         <v>0.7</v>
@@ -4589,19 +4512,19 @@
         <v>400</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="L12" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M12" s="9">
         <v>0</v>
@@ -4610,13 +4533,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O12" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P12" s="25">
+      <c r="O12" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P12" s="24">
         <v>6</v>
       </c>
-      <c r="Q12" s="25">
+      <c r="Q12" s="24">
         <f t="shared" si="4"/>
         <v>864</v>
       </c>
@@ -4624,11 +4547,11 @@
         <f t="shared" si="5"/>
         <v>864</v>
       </c>
-      <c r="S12" s="30">
+      <c r="S12" s="27">
         <v>1107</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U12" s="9"/>
       <c r="V12" s="20"/>
@@ -4641,21 +4564,21 @@
         <v/>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="29">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E13" s="16">
         <v>0.7</v>
@@ -4668,19 +4591,19 @@
         <v>400</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I13" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="L13" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M13" s="9">
         <v>0</v>
@@ -4689,13 +4612,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O13" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P13" s="25">
+      <c r="O13" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" s="24">
         <v>2</v>
       </c>
-      <c r="Q13" s="25">
+      <c r="Q13" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
@@ -4703,11 +4626,11 @@
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S13" s="30">
+      <c r="S13" s="27">
         <v>740</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U13" s="9"/>
       <c r="V13" s="20"/>
@@ -4720,21 +4643,21 @@
         <v/>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="29">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E14" s="16">
         <v>0.7</v>
@@ -4747,19 +4670,19 @@
         <v>400</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="J14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="L14" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M14" s="9">
         <v>0</v>
@@ -4768,13 +4691,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O14" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P14" s="25">
+      <c r="O14" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P14" s="24">
         <v>3</v>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="24">
         <f t="shared" si="4"/>
         <v>432</v>
       </c>
@@ -4782,11 +4705,11 @@
         <f t="shared" si="5"/>
         <v>432</v>
       </c>
-      <c r="S14" s="30">
+      <c r="S14" s="27">
         <v>865</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U14" s="9"/>
       <c r="V14" s="20"/>
@@ -4799,21 +4722,21 @@
         <v/>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="29">
       <c r="A15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E15" s="16">
         <v>0</v>
@@ -4829,16 +4752,16 @@
         <v>26</v>
       </c>
       <c r="I15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L15" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M15" s="9">
         <v>0</v>
@@ -4847,13 +4770,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O15" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P15" s="25">
+      <c r="O15" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P15" s="24">
         <v>2</v>
       </c>
-      <c r="Q15" s="25">
+      <c r="Q15" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
@@ -4861,11 +4784,11 @@
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S15" s="30">
+      <c r="S15" s="27">
         <v>403</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U15" s="9"/>
       <c r="V15" s="20"/>
@@ -4878,21 +4801,21 @@
         <v/>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="29">
       <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E16" s="16">
         <v>0</v>
@@ -4905,19 +4828,19 @@
         <v>50</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I16" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J16" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>112</v>
-      </c>
       <c r="L16" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M16" s="9">
         <v>0</v>
@@ -4926,13 +4849,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O16" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P16" s="25">
+      <c r="O16" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P16" s="24">
         <v>1</v>
       </c>
-      <c r="Q16" s="25">
+      <c r="Q16" s="24">
         <f t="shared" si="4"/>
         <v>144</v>
       </c>
@@ -4940,11 +4863,11 @@
         <f t="shared" si="5"/>
         <v>144</v>
       </c>
-      <c r="S16" s="30">
+      <c r="S16" s="27">
         <v>403</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U16" s="9"/>
       <c r="V16" s="20"/>
@@ -4957,21 +4880,21 @@
         <v/>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="29">
       <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="E17" s="16">
         <v>0.7</v>
@@ -4984,19 +4907,19 @@
         <v>400</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>127</v>
-      </c>
       <c r="L17" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M17" s="9">
         <v>0</v>
@@ -5005,13 +4928,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O17" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P17" s="25">
+      <c r="O17" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P17" s="24">
         <v>4</v>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
@@ -5019,11 +4942,11 @@
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S17" s="30">
+      <c r="S17" s="27">
         <v>1069</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U17" s="9"/>
       <c r="V17" s="20"/>
@@ -5036,21 +4959,21 @@
         <v/>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="29">
       <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E18" s="16">
         <v>0.7</v>
@@ -5063,19 +4986,19 @@
         <v>400</v>
       </c>
       <c r="H18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="J18" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="L18" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M18" s="9">
         <v>0</v>
@@ -5084,13 +5007,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O18" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P18" s="25">
+      <c r="O18" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P18" s="24">
         <v>2</v>
       </c>
-      <c r="Q18" s="25">
+      <c r="Q18" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
@@ -5098,11 +5021,11 @@
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S18" s="30">
+      <c r="S18" s="27">
         <v>854</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="20"/>
@@ -5115,21 +5038,21 @@
         <v/>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="29">
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E19" s="16">
         <v>0</v>
@@ -5145,16 +5068,16 @@
         <v>26</v>
       </c>
       <c r="I19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="L19" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M19" s="9">
         <v>0</v>
@@ -5163,13 +5086,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O19" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P19" s="25">
+      <c r="O19" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P19" s="24">
         <v>6</v>
       </c>
-      <c r="Q19" s="25">
+      <c r="Q19" s="24">
         <f t="shared" si="4"/>
         <v>864</v>
       </c>
@@ -5177,11 +5100,11 @@
         <f t="shared" si="5"/>
         <v>864</v>
       </c>
-      <c r="S19" s="30">
+      <c r="S19" s="27">
         <v>538</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U19" s="9"/>
       <c r="V19" s="20"/>
@@ -5194,21 +5117,21 @@
         <v/>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="29">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E20" s="16">
         <v>0.7</v>
@@ -5221,19 +5144,19 @@
         <v>400</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J20" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="L20" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M20" s="9">
         <v>0</v>
@@ -5242,13 +5165,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O20" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P20" s="25">
+      <c r="O20" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P20" s="24">
         <v>4</v>
       </c>
-      <c r="Q20" s="25">
+      <c r="Q20" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
@@ -5256,11 +5179,11 @@
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S20" s="30">
+      <c r="S20" s="27">
         <v>1064</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U20" s="9"/>
       <c r="V20" s="20"/>
@@ -5273,21 +5196,21 @@
         <v/>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="29">
       <c r="A21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E21" s="16">
         <v>0.7</v>
@@ -5300,19 +5223,19 @@
         <v>400</v>
       </c>
       <c r="H21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="J21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="L21" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M21" s="9">
         <v>0</v>
@@ -5321,13 +5244,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P21" s="25">
+      <c r="O21" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P21" s="24">
         <v>1</v>
       </c>
-      <c r="Q21" s="25">
+      <c r="Q21" s="24">
         <f t="shared" si="4"/>
         <v>144</v>
       </c>
@@ -5335,11 +5258,11 @@
         <f t="shared" si="5"/>
         <v>144</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="27">
         <v>538</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U21" s="9"/>
       <c r="V21" s="20"/>
@@ -5352,21 +5275,21 @@
         <v/>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="29">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E22" s="16">
         <v>0.7</v>
@@ -5379,19 +5302,19 @@
         <v>400</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I22" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="L22" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M22" s="9">
         <v>0</v>
@@ -5400,13 +5323,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O22" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P22" s="25">
+      <c r="O22" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P22" s="24">
         <v>4</v>
       </c>
-      <c r="Q22" s="25">
+      <c r="Q22" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
@@ -5414,11 +5337,11 @@
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="27">
         <v>1133</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U22" s="9"/>
       <c r="V22" s="20"/>
@@ -5431,21 +5354,21 @@
         <v/>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="29">
       <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E23" s="16">
         <v>0.7</v>
@@ -5458,19 +5381,19 @@
         <v>400</v>
       </c>
       <c r="H23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="J23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="L23" s="9" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="M23" s="9">
         <v>0</v>
@@ -5479,13 +5402,13 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O23" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="P23" s="25">
+      <c r="O23" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P23" s="24">
         <v>2</v>
       </c>
-      <c r="Q23" s="25">
+      <c r="Q23" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
@@ -5493,11 +5416,11 @@
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S23" s="30">
+      <c r="S23" s="27">
         <v>900</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U23" s="9"/>
       <c r="V23" s="20"/>
@@ -5510,15 +5433,15 @@
         <v/>
       </c>
       <c r="Y23" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="29">
       <c r="A24" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>24</v>
@@ -5549,22 +5472,34 @@
         <v>29</v>
       </c>
       <c r="L24" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M24" s="9">
+        <v>1</v>
+      </c>
+      <c r="N24" s="20">
+        <f>72*M24</f>
+        <v>72</v>
+      </c>
+      <c r="O24" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P24" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="20">
+        <f>N24</f>
+        <v>72</v>
+      </c>
+      <c r="S24" s="33">
+        <v>229</v>
+      </c>
+      <c r="T24" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="M24" s="9"/>
-      <c r="N24" s="20">
-        <v>72</v>
-      </c>
-      <c r="O24" s="25"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="20" t="str">
-        <f t="shared" ref="R24:R37" si="9">IF(OR(M24="",N24=""),"",M24*N24)</f>
-        <v/>
-      </c>
-      <c r="S24" s="30"/>
-      <c r="T24" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="U24" s="9"/>
       <c r="V24" s="20"/>
@@ -5577,155 +5512,179 @@
         <v/>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="29">
       <c r="A25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>135</v>
+        <v>78</v>
+      </c>
+      <c r="B25" s="30">
+        <v>202</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="E25" s="16">
         <v>0</v>
       </c>
       <c r="F25" s="18">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G25" s="18">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <f t="shared" ref="G25" si="9">ROUND(F25/0.8,0)</f>
+        <v>50</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="L25" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M25" s="9">
+        <v>2</v>
+      </c>
+      <c r="N25" s="20">
+        <f t="shared" ref="N25:N38" si="10">72*M25</f>
+        <v>144</v>
+      </c>
+      <c r="O25" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P25" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="24">
+        <f t="shared" ref="Q25:Q34" si="11">4*36*P25</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="20">
+        <f t="shared" ref="R25:R38" si="12">N25</f>
+        <v>144</v>
+      </c>
+      <c r="S25" s="33">
+        <v>168</v>
+      </c>
+      <c r="T25" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="M25" s="9"/>
-      <c r="N25" s="20">
-        <v>72</v>
-      </c>
-      <c r="O25" s="25"/>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S25" s="30"/>
-      <c r="T25" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="U25" s="9"/>
       <c r="V25" s="20"/>
       <c r="W25" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="W25" si="13">IF(OR(U25="",V25=""),"",U25*V25)</f>
         <v/>
       </c>
       <c r="X25" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="X25" si="14">IF(OR(R25="",W25=""),"",R25-W25)</f>
         <v/>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="29">
       <c r="A26" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="16">
+        <v>0</v>
+      </c>
+      <c r="F26" s="18">
         <v>80</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="F26" s="18">
-        <v>320</v>
-      </c>
       <c r="G26" s="18">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f>ROUND(F26/0.8,0)</f>
+        <v>100</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M26" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
       <c r="N26" s="20">
-        <v>144</v>
-      </c>
-      <c r="O26" s="25"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S26" s="30"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P26" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="20">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="33">
+        <v>0</v>
+      </c>
       <c r="T26" s="9" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="U26" s="9"/>
       <c r="V26" s="20"/>
       <c r="W26" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U26="",V26=""),"",U26*V26)</f>
         <v/>
       </c>
       <c r="X26" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R26="",W26=""),"",R26-W26)</f>
         <v/>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="29">
       <c r="A27" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>51</v>
+        <v>136</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>52</v>
+        <v>137</v>
       </c>
       <c r="E27" s="16">
         <v>0.7</v>
@@ -5734,65 +5693,77 @@
         <v>320</v>
       </c>
       <c r="G27" s="18">
-        <f t="shared" si="0"/>
+        <f>ROUND(F27/0.8,0)</f>
         <v>400</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K27" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M27" s="9">
+        <v>4</v>
+      </c>
+      <c r="N27" s="20">
+        <f>72*M27</f>
+        <v>288</v>
+      </c>
+      <c r="O27" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P27" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="20">
+        <f t="shared" si="12"/>
+        <v>288</v>
+      </c>
+      <c r="S27" s="33">
+        <v>291</v>
+      </c>
+      <c r="T27" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="20">
-        <v>144</v>
-      </c>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S27" s="30"/>
-      <c r="T27" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="U27" s="9"/>
       <c r="V27" s="20"/>
       <c r="W27" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U27="",V27=""),"",U27*V27)</f>
         <v/>
       </c>
       <c r="X27" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R27="",W27=""),"",R27-W27)</f>
         <v/>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="29">
       <c r="A28" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="E28" s="16">
         <v>0.7</v>
@@ -5801,199 +5772,235 @@
         <v>320</v>
       </c>
       <c r="G28" s="18">
-        <f t="shared" si="0"/>
+        <f>ROUND(F28/0.8,0)</f>
         <v>400</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="J28" s="8" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M28" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M28" s="9">
+        <v>4</v>
+      </c>
       <c r="N28" s="20">
-        <v>144</v>
-      </c>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S28" s="30"/>
+        <f t="shared" si="10"/>
+        <v>288</v>
+      </c>
+      <c r="O28" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P28" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="20">
+        <f t="shared" si="12"/>
+        <v>288</v>
+      </c>
+      <c r="S28" s="33">
+        <v>384</v>
+      </c>
       <c r="T28" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U28" s="9"/>
       <c r="V28" s="20"/>
       <c r="W28" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U28="",V28=""),"",U28*V28)</f>
         <v/>
       </c>
       <c r="X28" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R28="",W28=""),"",R28-W28)</f>
         <v/>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="29">
       <c r="A29" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>140</v>
+        <v>68</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="E29" s="16">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="F29" s="18">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="G29" s="18">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f>ROUND(F29/0.8,0)</f>
+        <v>400</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>142</v>
+        <v>52</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M29" s="9">
+        <v>5</v>
+      </c>
       <c r="N29" s="20">
-        <v>72</v>
-      </c>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S29" s="30"/>
+        <f t="shared" si="10"/>
+        <v>360</v>
+      </c>
+      <c r="O29" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P29" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="20">
+        <f t="shared" si="12"/>
+        <v>360</v>
+      </c>
+      <c r="S29" s="33">
+        <v>375</v>
+      </c>
       <c r="T29" s="9" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="U29" s="9"/>
       <c r="V29" s="20"/>
       <c r="W29" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U29="",V29=""),"",U29*V29)</f>
         <v/>
       </c>
       <c r="X29" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R29="",W29=""),"",R29-W29)</f>
         <v/>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="29">
       <c r="A30" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="E30" s="16">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F30" s="18">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="G30" s="18">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f>ROUND(F30/0.8,0)</f>
+        <v>200</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M30" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M30" s="9">
+        <v>7</v>
+      </c>
       <c r="N30" s="20">
-        <v>144</v>
-      </c>
-      <c r="O30" s="25"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="25"/>
-      <c r="R30" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S30" s="30"/>
+        <f t="shared" si="10"/>
+        <v>504</v>
+      </c>
+      <c r="O30" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P30" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="20">
+        <f t="shared" si="12"/>
+        <v>504</v>
+      </c>
+      <c r="S30" s="33">
+        <v>316</v>
+      </c>
       <c r="T30" s="9" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="U30" s="9"/>
       <c r="V30" s="20"/>
       <c r="W30" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U30="",V30=""),"",U30*V30)</f>
         <v/>
       </c>
       <c r="X30" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R30="",W30=""),"",R30-W30)</f>
         <v/>
       </c>
       <c r="Y30" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="29">
       <c r="A31" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E31" s="16">
         <v>0.7</v>
@@ -6002,454 +6009,643 @@
         <v>320</v>
       </c>
       <c r="G31" s="18">
-        <f t="shared" si="0"/>
+        <f>ROUND(F31/0.8,0)</f>
         <v>400</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K31" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M31" s="9">
+        <v>9</v>
+      </c>
+      <c r="N31" s="20">
+        <f t="shared" si="10"/>
+        <v>648</v>
+      </c>
+      <c r="O31" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P31" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="20">
+        <f t="shared" si="12"/>
+        <v>648</v>
+      </c>
+      <c r="S31" s="33">
+        <v>476</v>
+      </c>
+      <c r="T31" s="9" t="s">
         <v>56</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M31" s="9"/>
-      <c r="N31" s="20">
-        <v>144</v>
-      </c>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S31" s="30"/>
-      <c r="T31" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="U31" s="9"/>
       <c r="V31" s="20"/>
       <c r="W31" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U31="",V31=""),"",U31*V31)</f>
         <v/>
       </c>
       <c r="X31" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R31="",W31=""),"",R31-W31)</f>
         <v/>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="29">
       <c r="A32" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E32" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F32" s="18">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="G32" s="18">
         <f>ROUND(F32/0.8,0)</f>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M32" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M32" s="9">
+        <v>6</v>
+      </c>
       <c r="N32" s="20">
-        <v>72</v>
-      </c>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S32" s="30"/>
+        <f t="shared" si="10"/>
+        <v>432</v>
+      </c>
+      <c r="O32" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P32" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="20">
+        <f t="shared" si="12"/>
+        <v>432</v>
+      </c>
+      <c r="S32" s="33">
+        <v>552</v>
+      </c>
       <c r="T32" s="9" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="U32" s="9"/>
       <c r="V32" s="20"/>
       <c r="W32" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U32="",V32=""),"",U32*V32)</f>
         <v/>
       </c>
       <c r="X32" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R32="",W32=""),"",R32-W32)</f>
         <v/>
       </c>
       <c r="Y32" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="29">
       <c r="A33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="16">
+        <v>0</v>
+      </c>
+      <c r="F33" s="18">
         <v>80</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="F33" s="18">
-        <v>320</v>
-      </c>
       <c r="G33" s="18">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f>ROUND(F33/0.8,0)</f>
+        <v>100</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M33" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M33" s="9">
+        <v>2</v>
+      </c>
       <c r="N33" s="20">
+        <f t="shared" si="10"/>
         <v>144</v>
       </c>
-      <c r="O33" s="25"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S33" s="30"/>
+      <c r="O33" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P33" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="24">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="20">
+        <f t="shared" si="12"/>
+        <v>144</v>
+      </c>
+      <c r="S33" s="33">
+        <v>227</v>
+      </c>
       <c r="T33" s="9" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="U33" s="9"/>
       <c r="V33" s="20"/>
       <c r="W33" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U33="",V33=""),"",U33*V33)</f>
         <v/>
       </c>
       <c r="X33" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R33="",W33=""),"",R33-W33)</f>
         <v/>
       </c>
       <c r="Y33" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="29">
       <c r="A34" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E34" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F34" s="18">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="G34" s="18">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <f>ROUND(F34/0.8,0)</f>
+        <v>400</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M34" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M34" s="9">
+        <v>9</v>
+      </c>
       <c r="N34" s="20">
-        <v>72</v>
-      </c>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S34" s="30"/>
+        <f t="shared" si="10"/>
+        <v>648</v>
+      </c>
+      <c r="O34" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P34" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="24">
+        <f>4*36*P34</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="20">
+        <f t="shared" si="12"/>
+        <v>648</v>
+      </c>
+      <c r="S34" s="33">
+        <v>676</v>
+      </c>
       <c r="T34" s="9" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="U34" s="9"/>
       <c r="V34" s="20"/>
       <c r="W34" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U34="",V34=""),"",U34*V34)</f>
         <v/>
       </c>
       <c r="X34" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R34="",W34=""),"",R34-W34)</f>
         <v/>
       </c>
       <c r="Y34" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" ht="29">
       <c r="A35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E35" s="16">
+        <v>0</v>
+      </c>
+      <c r="F35" s="18">
         <v>80</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="F35" s="18">
-        <v>320</v>
-      </c>
       <c r="G35" s="18">
-        <f t="shared" si="0"/>
-        <v>400</v>
+        <f>ROUND(F35/0.8,0)</f>
+        <v>100</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M35" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M35" s="9">
+        <v>3</v>
+      </c>
       <c r="N35" s="20">
-        <v>144</v>
-      </c>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S35" s="30"/>
+        <f>72*M35</f>
+        <v>216</v>
+      </c>
+      <c r="O35" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P35" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="24">
+        <f t="shared" ref="Q35:Q38" si="15">4*36*P35</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="20">
+        <f>N35</f>
+        <v>216</v>
+      </c>
+      <c r="S35" s="33">
+        <v>273</v>
+      </c>
       <c r="T35" s="9" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="U35" s="9"/>
       <c r="V35" s="20"/>
       <c r="W35" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U35="",V35=""),"",U35*V35)</f>
         <v/>
       </c>
       <c r="X35" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R35="",W35=""),"",R35-W35)</f>
         <v/>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="29">
       <c r="A36" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>137</v>
+        <v>69</v>
       </c>
       <c r="E36" s="16">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F36" s="18">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="G36" s="18">
-        <f t="shared" si="0"/>
-        <v>100</v>
+        <f>ROUND(F36/0.8,0)</f>
+        <v>400</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M36" s="9"/>
+        <v>190</v>
+      </c>
+      <c r="M36" s="9">
+        <v>8</v>
+      </c>
       <c r="N36" s="20">
-        <v>72</v>
-      </c>
-      <c r="O36" s="25"/>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="20" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S36" s="30"/>
+        <f t="shared" si="10"/>
+        <v>576</v>
+      </c>
+      <c r="O36" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P36" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="24">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="20">
+        <f t="shared" si="12"/>
+        <v>576</v>
+      </c>
+      <c r="S36" s="33">
+        <v>622</v>
+      </c>
       <c r="T36" s="9" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="U36" s="9"/>
       <c r="V36" s="20"/>
       <c r="W36" s="20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(OR(U36="",V36=""),"",U36*V36)</f>
         <v/>
       </c>
       <c r="X36" s="20" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(R36="",W36=""),"",R36-W36)</f>
         <v/>
       </c>
       <c r="Y36" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" ht="25.5">
-      <c r="A37" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="29">
+      <c r="A37" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" s="16">
+        <v>0</v>
+      </c>
+      <c r="F37" s="18">
         <v>80</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E37" s="17">
+      <c r="G37" s="18">
+        <f>ROUND(F37/0.8,0)</f>
+        <v>100</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M37" s="9">
+        <v>1</v>
+      </c>
+      <c r="N37" s="20">
+        <f t="shared" si="10"/>
+        <v>72</v>
+      </c>
+      <c r="O37" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P37" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="24">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="20">
+        <f t="shared" si="12"/>
+        <v>72</v>
+      </c>
+      <c r="S37" s="33">
+        <v>136</v>
+      </c>
+      <c r="T37" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="U37" s="9"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20" t="str">
+        <f>IF(OR(U37="",V37=""),"",U37*V37)</f>
+        <v/>
+      </c>
+      <c r="X37" s="20" t="str">
+        <f>IF(OR(R37="",W37=""),"",R37-W37)</f>
+        <v/>
+      </c>
+      <c r="Y37" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="29">
+      <c r="A38" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="17">
         <v>0.7</v>
       </c>
-      <c r="F37" s="19">
+      <c r="F38" s="19">
         <v>320</v>
       </c>
-      <c r="G37" s="19">
-        <f t="shared" si="0"/>
+      <c r="G38" s="19">
+        <f>ROUND(F38/0.8,0)</f>
         <v>400</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H38" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I38" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="J38" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="K38" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="K37" s="13" t="s">
+      <c r="L38" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="M38" s="14">
+        <v>8</v>
+      </c>
+      <c r="N38" s="20">
+        <f t="shared" si="10"/>
+        <v>576</v>
+      </c>
+      <c r="O38" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="P38" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="24">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="20">
+        <f t="shared" si="12"/>
+        <v>576</v>
+      </c>
+      <c r="S38" s="33">
+        <v>458</v>
+      </c>
+      <c r="T38" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="L37" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="M37" s="14"/>
-      <c r="N37" s="21">
-        <v>144</v>
-      </c>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="21" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S37" s="30"/>
-      <c r="T37" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="U37" s="14"/>
-      <c r="V37" s="21"/>
-      <c r="W37" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="X37" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y37" s="15" t="s">
-        <v>32</v>
-      </c>
+      <c r="U38" s="14"/>
+      <c r="V38" s="21"/>
+      <c r="W38" s="21" t="str">
+        <f>IF(OR(U38="",V38=""),"",U38*V38)</f>
+        <v/>
+      </c>
+      <c r="X38" s="21" t="str">
+        <f>IF(OR(R38="",W38=""),"",R38-W38)</f>
+        <v/>
+      </c>
+      <c r="Y38" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
+      <c r="L39" s="31"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="32"/>
+    </row>
+    <row r="40" spans="1:25">
+      <c r="L40" s="31"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+    </row>
+    <row r="41" spans="1:25">
+      <c r="L41" s="31"/>
+      <c r="O41" s="32"/>
+      <c r="P41" s="32"/>
+    </row>
+    <row r="42" spans="1:25">
+      <c r="L42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="L43" s="32"/>
+    </row>
+    <row r="44" spans="1:25">
+      <c r="L44" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6457,11 +6653,19 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="S4:S23">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$S4&gt;=$F4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$S4&lt;$F4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S25">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$S25&gt;=$F25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$S25&lt;$F25</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6472,7 +6676,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -6480,47 +6684,47 @@
     <col min="6" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:8" ht="21">
+      <c r="A1" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+    </row>
+    <row r="2" spans="1:8" ht="32">
+      <c r="A2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" spans="1:8" ht="30">
-      <c r="A2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.5">
+    </row>
+    <row r="3" spans="1:8" ht="32">
       <c r="A3" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" s="22">
         <v>0.7</v>
@@ -6533,21 +6737,21 @@
         <v>400</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F3" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="32">
+      <c r="A4" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.5">
-      <c r="A4" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="B4" s="22">
         <v>0.7</v>
@@ -6560,21 +6764,21 @@
         <v>400</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F4" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="H4" s="23" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:8" ht="16">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B5" s="22">
         <v>0.7</v>
@@ -6587,21 +6791,21 @@
         <v>400</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B6" s="22">
         <v>0</v>
@@ -6617,16 +6821,16 @@
         <v>26</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -6644,18 +6848,18 @@
         <v>26</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G7" s="23" t="s">
         <v>28</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16">
       <c r="A8" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B8" s="22">
         <v>0</v>
@@ -6668,21 +6872,21 @@
         <v>100</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16">
+      <c r="A9" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="B9" s="22">
         <v>0</v>
@@ -6695,21 +6899,21 @@
         <v>100</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="G9" s="23" t="s">
+    </row>
+    <row r="10" spans="1:8" ht="32">
+      <c r="A10" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.5">
-      <c r="A10" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="B10" s="22">
         <v>0</v>
@@ -6722,21 +6926,21 @@
         <v>200</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="16">
       <c r="A11" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B11" s="22">
         <v>0.85</v>
@@ -6749,21 +6953,21 @@
         <v>200</v>
       </c>
       <c r="E11" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="H11" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16">
+      <c r="A12" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="B12" s="22">
         <v>0.85</v>
@@ -6776,16 +6980,16 @@
         <v>300</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/excel/Building A B Lighting New.xlsx
+++ b/excel/Building A B Lighting New.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pacopoon/Downloads/Alpha_Design_17/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\310_Project1\Alpha_Design_17\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F837A4F-C3CE-C444-90DA-145521EAE380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C1890B5-0704-49E0-8B49-07AA063E7017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Building A" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="197">
   <si>
     <t>Building A — Lighting Place Schedule</t>
   </si>
@@ -611,13 +611,28 @@
   </si>
   <si>
     <t>Philips 4x36W SLB</t>
+  </si>
+  <si>
+    <t>UGR Restriction (Max)</t>
+  </si>
+  <si>
+    <t>No specific UGR; control glare</t>
+  </si>
+  <si>
+    <t>≤ 22</t>
+  </si>
+  <si>
+    <t>≤ 19</t>
+  </si>
+  <si>
+    <t>≤ 25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -642,8 +657,22 @@
       <sz val="8"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,6 +718,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -765,10 +805,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -849,25 +894,41 @@
     <xf numFmtId="1" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="9" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="3" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{2AA92BEB-B410-4070-B401-92FCF13F382F}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{1E9D80B0-E65E-4057-BA4F-9249344BC5A1}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{E1901BDC-6B84-4E66-86D1-52AE3CA3FF63}"/>
+    <cellStyle name="Normal 5" xfId="4" xr:uid="{ED6D2035-F9DA-4B1D-B2ED-B5DB87628F59}"/>
+    <cellStyle name="Normal 6" xfId="5" xr:uid="{FCC80704-4661-421C-AAE8-B6CB6410940C}"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1079,53 +1140,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:Z36"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="34" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="8.33203125" customWidth="1"/>
-    <col min="17" max="19" width="12" customWidth="1"/>
-    <col min="20" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="8" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="8.296875" customWidth="1"/>
+    <col min="18" max="20" width="12" customWidth="1"/>
+    <col min="21" max="22" width="14" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-    </row>
-    <row r="2" spans="1:25" ht="48">
+    <row r="1" spans="1:26" ht="21">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+    </row>
+    <row r="2" spans="1:26" ht="41.4">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1150,59 +1212,62 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="T2" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="29">
+    <row r="3" spans="1:26" ht="27.6">
       <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
@@ -1228,52 +1293,55 @@
       <c r="H3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M3" s="9">
+      <c r="N3" s="9">
         <v>1</v>
       </c>
-      <c r="N3" s="20">
+      <c r="O3" s="20">
         <v>72</v>
       </c>
-      <c r="O3" s="24"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="24"/>
-      <c r="R3" s="20">
-        <f>IF(OR(M3="",N3=""),"",M3*N3)</f>
+      <c r="R3" s="24"/>
+      <c r="S3" s="20">
+        <f>IF(OR(N3="",O3=""),"",N3*O3)</f>
         <v>72</v>
       </c>
-      <c r="S3" s="27" t="s">
+      <c r="T3" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U3" s="9"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20" t="str">
-        <f>IF(OR(U3="",V3=""),"",U3*V3)</f>
-        <v/>
-      </c>
+      <c r="V3" s="9"/>
+      <c r="W3" s="20"/>
       <c r="X3" s="20" t="str">
-        <f t="shared" ref="X3:X36" si="1">IF(OR(R3="",W3=""),"",R3-W3)</f>
-        <v/>
-      </c>
-      <c r="Y3" s="10" t="s">
+        <f>IF(OR(V3="",W3=""),"",V3*W3)</f>
+        <v/>
+      </c>
+      <c r="Y3" s="20" t="str">
+        <f t="shared" ref="Y3:Y36" si="1">IF(OR(S3="",X3=""),"",S3-X3)</f>
+        <v/>
+      </c>
+      <c r="Z3" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="29">
+    <row r="4" spans="1:26" ht="27.6">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -1299,59 +1367,62 @@
       <c r="H4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M4" s="9">
+      <c r="N4" s="9">
         <v>2</v>
       </c>
-      <c r="N4" s="20">
+      <c r="O4" s="20">
         <v>72</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="P4" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P4" s="24">
+      <c r="Q4" s="24">
         <v>5</v>
       </c>
-      <c r="Q4" s="24">
+      <c r="R4" s="24">
         <f>4*36</f>
         <v>144</v>
       </c>
-      <c r="R4" s="20">
-        <f>IF(OR(M4="",N4=""),"",M4*N4+Q4)</f>
+      <c r="S4" s="20">
+        <f>IF(OR(N4="",O4=""),"",N4*O4+R4)</f>
         <v>288</v>
       </c>
-      <c r="S4" s="27">
+      <c r="T4" s="27">
         <v>503</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20" t="str">
-        <f>IF(OR(U4="",V4=""),"",U4*V4)</f>
-        <v/>
-      </c>
+      <c r="V4" s="9"/>
+      <c r="W4" s="20"/>
       <c r="X4" s="20" t="str">
+        <f>IF(OR(V4="",W4=""),"",V4*W4)</f>
+        <v/>
+      </c>
+      <c r="Y4" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Z4" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="29">
+    <row r="5" spans="1:26" ht="26.4">
       <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
@@ -1377,52 +1448,55 @@
       <c r="H5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M5" s="9">
+      <c r="N5" s="9">
         <v>1</v>
       </c>
-      <c r="N5" s="20">
+      <c r="O5" s="20">
         <v>72</v>
       </c>
-      <c r="O5" s="25"/>
-      <c r="P5" s="24"/>
+      <c r="P5" s="25"/>
       <c r="Q5" s="24"/>
-      <c r="R5" s="20">
-        <f t="shared" ref="R5:R35" si="2">IF(OR(M5="",N5=""),"",M5*N5)</f>
+      <c r="R5" s="24"/>
+      <c r="S5" s="20">
+        <f t="shared" ref="S5:S35" si="2">IF(OR(N5="",O5=""),"",N5*O5)</f>
         <v>72</v>
       </c>
-      <c r="S5" s="27">
+      <c r="T5" s="27">
         <v>209</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="U5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="9"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20" t="str">
-        <f t="shared" ref="W5:W36" si="3">IF(OR(U5="",V5=""),"",U5*V5)</f>
-        <v/>
-      </c>
+      <c r="V5" s="9"/>
+      <c r="W5" s="20"/>
       <c r="X5" s="20" t="str">
+        <f t="shared" ref="X5:X36" si="3">IF(OR(V5="",W5=""),"",V5*W5)</f>
+        <v/>
+      </c>
+      <c r="Y5" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Z5" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="29">
+    <row r="6" spans="1:26" ht="26.4">
       <c r="A6" s="6" t="s">
         <v>22</v>
       </c>
@@ -1448,52 +1522,55 @@
       <c r="H6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M6" s="9">
+      <c r="N6" s="9">
         <v>1</v>
       </c>
-      <c r="N6" s="20">
+      <c r="O6" s="20">
         <v>72</v>
       </c>
-      <c r="O6" s="24"/>
       <c r="P6" s="24"/>
       <c r="Q6" s="24"/>
-      <c r="R6" s="20">
+      <c r="R6" s="24"/>
+      <c r="S6" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S6" s="27">
+      <c r="T6" s="27">
         <v>209</v>
       </c>
-      <c r="T6" s="9" t="s">
+      <c r="U6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U6" s="9"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20" t="str">
+      <c r="V6" s="9"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X6" s="20" t="str">
+      <c r="Y6" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Z6" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="29">
+    <row r="7" spans="1:26" ht="26.4">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
@@ -1519,52 +1596,55 @@
       <c r="H7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="M7" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M7" s="9">
+      <c r="N7" s="9">
         <v>1</v>
       </c>
-      <c r="N7" s="20">
+      <c r="O7" s="20">
         <v>72</v>
       </c>
-      <c r="O7" s="24"/>
       <c r="P7" s="24"/>
       <c r="Q7" s="24"/>
-      <c r="R7" s="20">
+      <c r="R7" s="24"/>
+      <c r="S7" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S7" s="27">
+      <c r="T7" s="27">
         <v>183</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U7" s="9"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20" t="str">
+      <c r="V7" s="9"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X7" s="20" t="str">
+      <c r="Y7" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y7" s="10" t="s">
+      <c r="Z7" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="29">
+    <row r="8" spans="1:26" ht="26.4">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
@@ -1590,52 +1670,55 @@
       <c r="H8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="M8" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M8" s="9">
+      <c r="N8" s="9">
         <v>2</v>
       </c>
-      <c r="N8" s="20">
+      <c r="O8" s="20">
         <v>144</v>
       </c>
-      <c r="O8" s="24"/>
       <c r="P8" s="24"/>
       <c r="Q8" s="24"/>
-      <c r="R8" s="20">
+      <c r="R8" s="24"/>
+      <c r="S8" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S8" s="27">
+      <c r="T8" s="27">
         <v>625</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U8" s="9"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20" t="str">
+      <c r="V8" s="9"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X8" s="20" t="str">
+      <c r="Y8" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="Z8" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="29">
+    <row r="9" spans="1:26" ht="26.4">
       <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
@@ -1661,52 +1744,55 @@
       <c r="H9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="M9" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M9" s="9">
+      <c r="N9" s="9">
         <v>2</v>
       </c>
-      <c r="N9" s="20">
+      <c r="O9" s="20">
         <v>144</v>
       </c>
-      <c r="O9" s="24"/>
       <c r="P9" s="24"/>
       <c r="Q9" s="24"/>
-      <c r="R9" s="20">
+      <c r="R9" s="24"/>
+      <c r="S9" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S9" s="27">
+      <c r="T9" s="27">
         <v>644</v>
       </c>
-      <c r="T9" s="9" t="s">
+      <c r="U9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U9" s="9"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20" t="str">
+      <c r="V9" s="9"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X9" s="20" t="str">
+      <c r="Y9" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y9" s="10" t="s">
+      <c r="Z9" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="29">
+    <row r="10" spans="1:26" ht="27.6">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -1732,59 +1818,62 @@
       <c r="H10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M10" s="9">
+      <c r="N10" s="9">
         <v>4</v>
       </c>
-      <c r="N10" s="20">
+      <c r="O10" s="20">
         <v>72</v>
       </c>
-      <c r="O10" s="25" t="s">
+      <c r="P10" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P10" s="24">
+      <c r="Q10" s="24">
         <v>4</v>
       </c>
-      <c r="Q10" s="24">
+      <c r="R10" s="24">
         <f>4*36</f>
         <v>144</v>
       </c>
-      <c r="R10" s="20">
-        <f>IF(OR(M10="",N10=""),"",M10*N10+Q10)</f>
+      <c r="S10" s="20">
+        <f>IF(OR(N10="",O10=""),"",N10*O10+R10)</f>
         <v>432</v>
       </c>
-      <c r="S10" s="27">
+      <c r="T10" s="27">
         <v>373</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="U10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U10" s="9"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20" t="str">
+      <c r="V10" s="9"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X10" s="20" t="str">
+      <c r="Y10" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y10" s="10" t="s">
+      <c r="Z10" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="29">
+    <row r="11" spans="1:26" ht="26.4">
       <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
@@ -1810,51 +1899,54 @@
       <c r="H11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="M11" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M11" s="9">
+      <c r="N11" s="9">
         <v>2</v>
       </c>
-      <c r="N11" s="20">
+      <c r="O11" s="20">
         <v>144</v>
       </c>
-      <c r="O11" s="24"/>
       <c r="P11" s="24"/>
       <c r="Q11" s="24"/>
-      <c r="R11" s="20">
+      <c r="R11" s="24"/>
+      <c r="S11" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S11" s="27">
+      <c r="T11" s="27">
         <v>615</v>
       </c>
-      <c r="T11" s="9" t="s">
+      <c r="U11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20" t="str">
-        <f>IF(OR(U12="",V11=""),"",U12*V11)</f>
-        <v/>
-      </c>
+      <c r="W11" s="20"/>
       <c r="X11" s="20" t="str">
+        <f>IF(OR(V12="",W11=""),"",V12*W11)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y11" s="10" t="s">
+      <c r="Z11" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="29">
+    <row r="12" spans="1:26" ht="26.4">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
@@ -1880,52 +1972,55 @@
       <c r="H12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="M12" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M12" s="9">
+      <c r="N12" s="9">
         <v>4</v>
       </c>
-      <c r="N12" s="20">
+      <c r="O12" s="20">
         <v>144</v>
       </c>
-      <c r="O12" s="24"/>
       <c r="P12" s="24"/>
       <c r="Q12" s="24"/>
-      <c r="R12" s="20">
+      <c r="R12" s="24"/>
+      <c r="S12" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S12" s="27">
+      <c r="T12" s="27">
         <v>836</v>
       </c>
-      <c r="T12" s="9" t="s">
+      <c r="U12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U12" s="9"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="20" t="e">
-        <f>IF(OR(#REF!="",V12=""),"",#REF!*V12)</f>
+      <c r="V12" s="9"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20" t="e">
+        <f>IF(OR(#REF!="",W12=""),"",#REF!*W12)</f>
         <v>#REF!</v>
       </c>
-      <c r="X12" s="20" t="e">
+      <c r="Y12" s="20" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="Y12" s="10" t="s">
+      <c r="Z12" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="29">
+    <row r="13" spans="1:26" ht="26.4">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
@@ -1951,52 +2046,55 @@
       <c r="H13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="25" t="s">
+      <c r="M13" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M13" s="9">
+      <c r="N13" s="9">
         <v>4</v>
       </c>
-      <c r="N13" s="20">
+      <c r="O13" s="20">
         <v>144</v>
       </c>
-      <c r="O13" s="24"/>
       <c r="P13" s="24"/>
       <c r="Q13" s="24"/>
-      <c r="R13" s="20">
+      <c r="R13" s="24"/>
+      <c r="S13" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S13" s="27">
+      <c r="T13" s="27">
         <v>743</v>
       </c>
-      <c r="T13" s="9" t="s">
+      <c r="U13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="20" t="str">
+      <c r="V13" s="9"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X13" s="20" t="str">
+      <c r="Y13" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y13" s="10" t="s">
+      <c r="Z13" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="29">
+    <row r="14" spans="1:26" ht="26.4">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
@@ -2022,52 +2120,55 @@
       <c r="H14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L14" s="25" t="s">
+      <c r="M14" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M14" s="9">
+      <c r="N14" s="9">
         <v>6</v>
       </c>
-      <c r="N14" s="20">
+      <c r="O14" s="20">
         <v>144</v>
       </c>
-      <c r="O14" s="24"/>
       <c r="P14" s="24"/>
       <c r="Q14" s="24"/>
-      <c r="R14" s="20">
+      <c r="R14" s="24"/>
+      <c r="S14" s="20">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="S14" s="27">
+      <c r="T14" s="27">
         <v>1088</v>
       </c>
-      <c r="T14" s="9" t="s">
+      <c r="U14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U14" s="9"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20" t="str">
+      <c r="V14" s="9"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X14" s="20" t="str">
+      <c r="Y14" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y14" s="10" t="s">
+      <c r="Z14" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="29">
+    <row r="15" spans="1:26" ht="26.4">
       <c r="A15" s="6" t="s">
         <v>22</v>
       </c>
@@ -2093,52 +2194,55 @@
       <c r="H15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L15" s="25" t="s">
+      <c r="M15" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M15" s="9">
+      <c r="N15" s="9">
         <v>3</v>
       </c>
-      <c r="N15" s="20">
+      <c r="O15" s="20">
         <v>144</v>
       </c>
-      <c r="O15" s="24"/>
       <c r="P15" s="24"/>
       <c r="Q15" s="24"/>
-      <c r="R15" s="20">
+      <c r="R15" s="24"/>
+      <c r="S15" s="20">
         <f t="shared" si="2"/>
         <v>432</v>
       </c>
-      <c r="S15" s="27">
+      <c r="T15" s="27">
         <v>743</v>
       </c>
-      <c r="T15" s="9" t="s">
+      <c r="U15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U15" s="9"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20" t="str">
+      <c r="V15" s="9"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X15" s="20" t="str">
+      <c r="Y15" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y15" s="10" t="s">
+      <c r="Z15" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="29">
+    <row r="16" spans="1:26" ht="26.4">
       <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
@@ -2164,52 +2268,55 @@
       <c r="H16" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L16" s="25" t="s">
+      <c r="M16" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="M16" s="9">
+      <c r="N16" s="9">
         <v>3</v>
       </c>
-      <c r="N16" s="20">
+      <c r="O16" s="20">
         <v>144</v>
       </c>
-      <c r="O16" s="24"/>
       <c r="P16" s="24"/>
       <c r="Q16" s="24"/>
-      <c r="R16" s="20">
+      <c r="R16" s="24"/>
+      <c r="S16" s="20">
         <f t="shared" si="2"/>
         <v>432</v>
       </c>
-      <c r="S16" s="27">
+      <c r="T16" s="27">
         <v>954</v>
       </c>
-      <c r="T16" s="9" t="s">
+      <c r="U16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U16" s="9"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20" t="str">
+      <c r="V16" s="9"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X16" s="20" t="str">
+      <c r="Y16" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y16" s="10" t="s">
+      <c r="Z16" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="29">
+    <row r="17" spans="1:26" ht="27.6">
       <c r="A17" s="6" t="s">
         <v>78</v>
       </c>
@@ -2235,52 +2342,55 @@
       <c r="H17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="M17" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M17" s="9">
+      <c r="N17" s="9">
         <v>1</v>
       </c>
-      <c r="N17" s="20">
+      <c r="O17" s="20">
         <v>72</v>
       </c>
-      <c r="O17" s="24"/>
       <c r="P17" s="24"/>
       <c r="Q17" s="24"/>
-      <c r="R17" s="20">
+      <c r="R17" s="24"/>
+      <c r="S17" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S17" s="27">
+      <c r="T17" s="27">
         <v>150</v>
       </c>
-      <c r="T17" s="9" t="s">
+      <c r="U17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U17" s="9"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20" t="str">
+      <c r="V17" s="9"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X17" s="20" t="str">
+      <c r="Y17" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y17" s="10" t="s">
+      <c r="Z17" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="29">
+    <row r="18" spans="1:26" ht="27.6">
       <c r="A18" s="6" t="s">
         <v>78</v>
       </c>
@@ -2306,52 +2416,55 @@
       <c r="H18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="M18" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M18" s="9">
+      <c r="N18" s="9">
         <v>4</v>
       </c>
-      <c r="N18" s="20">
+      <c r="O18" s="20">
         <v>72</v>
       </c>
-      <c r="O18" s="24"/>
       <c r="P18" s="24"/>
       <c r="Q18" s="24"/>
-      <c r="R18" s="20">
+      <c r="R18" s="24"/>
+      <c r="S18" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S18" s="27">
+      <c r="T18" s="27">
         <v>140</v>
       </c>
-      <c r="T18" s="9" t="s">
+      <c r="U18" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U18" s="9"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20" t="str">
+      <c r="V18" s="9"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X18" s="20" t="str">
+      <c r="Y18" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y18" s="10" t="s">
+      <c r="Z18" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="29">
+    <row r="19" spans="1:26" ht="26.4">
       <c r="A19" s="6" t="s">
         <v>78</v>
       </c>
@@ -2377,52 +2490,55 @@
       <c r="H19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="M19" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M19" s="9">
+      <c r="N19" s="9">
         <v>2</v>
       </c>
-      <c r="N19" s="20">
+      <c r="O19" s="20">
         <v>144</v>
       </c>
-      <c r="O19" s="24"/>
       <c r="P19" s="24"/>
       <c r="Q19" s="24"/>
-      <c r="R19" s="20">
+      <c r="R19" s="24"/>
+      <c r="S19" s="20">
         <f t="shared" si="2"/>
         <v>288</v>
       </c>
-      <c r="S19" s="27">
+      <c r="T19" s="27">
         <v>331</v>
       </c>
-      <c r="T19" s="9" t="s">
+      <c r="U19" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U19" s="9"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20" t="str">
+      <c r="V19" s="9"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X19" s="20" t="str">
+      <c r="Y19" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y19" s="10" t="s">
+      <c r="Z19" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="29">
+    <row r="20" spans="1:26" ht="26.4">
       <c r="A20" s="6" t="s">
         <v>78</v>
       </c>
@@ -2448,52 +2564,55 @@
       <c r="H20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="M20" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M20" s="9">
+      <c r="N20" s="9">
         <v>7</v>
       </c>
-      <c r="N20" s="20">
+      <c r="O20" s="20">
         <v>144</v>
       </c>
-      <c r="O20" s="24"/>
       <c r="P20" s="24"/>
       <c r="Q20" s="24"/>
-      <c r="R20" s="20">
+      <c r="R20" s="24"/>
+      <c r="S20" s="20">
         <f t="shared" si="2"/>
         <v>1008</v>
       </c>
-      <c r="S20" s="27">
+      <c r="T20" s="27">
         <v>470</v>
       </c>
-      <c r="T20" s="9" t="s">
+      <c r="U20" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U20" s="9"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20" t="str">
+      <c r="V20" s="9"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X20" s="20" t="str">
+      <c r="Y20" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y20" s="10" t="s">
+      <c r="Z20" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="29">
+    <row r="21" spans="1:26" ht="27.6">
       <c r="A21" s="6" t="s">
         <v>78</v>
       </c>
@@ -2519,52 +2638,55 @@
       <c r="H21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="M21" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M21" s="9">
+      <c r="N21" s="9">
         <v>1</v>
       </c>
-      <c r="N21" s="20">
+      <c r="O21" s="20">
         <v>72</v>
       </c>
-      <c r="O21" s="24"/>
       <c r="P21" s="24"/>
       <c r="Q21" s="24"/>
-      <c r="R21" s="20">
+      <c r="R21" s="24"/>
+      <c r="S21" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S21" s="27">
+      <c r="T21" s="27">
         <v>181</v>
       </c>
-      <c r="T21" s="9" t="s">
+      <c r="U21" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U21" s="9"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20" t="str">
+      <c r="V21" s="9"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X21" s="20" t="str">
+      <c r="Y21" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y21" s="10" t="s">
+      <c r="Z21" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="29">
+    <row r="22" spans="1:26" ht="26.4">
       <c r="A22" s="6" t="s">
         <v>78</v>
       </c>
@@ -2590,52 +2712,55 @@
       <c r="H22" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M22" s="9">
+      <c r="N22" s="9">
         <v>2</v>
       </c>
-      <c r="N22" s="20">
+      <c r="O22" s="20">
         <v>72</v>
       </c>
-      <c r="O22" s="24"/>
       <c r="P22" s="24"/>
       <c r="Q22" s="24"/>
-      <c r="R22" s="20">
+      <c r="R22" s="24"/>
+      <c r="S22" s="20">
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="S22" s="27">
+      <c r="T22" s="27">
         <v>269</v>
       </c>
-      <c r="T22" s="9" t="s">
+      <c r="U22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U22" s="9"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20" t="str">
+      <c r="V22" s="9"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X22" s="20" t="str">
+      <c r="Y22" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y22" s="10" t="s">
+      <c r="Z22" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="29">
+    <row r="23" spans="1:26" ht="26.4">
       <c r="A23" s="6" t="s">
         <v>78</v>
       </c>
@@ -2661,52 +2786,55 @@
       <c r="H23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="M23" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M23" s="9">
+      <c r="N23" s="9">
         <v>6</v>
       </c>
-      <c r="N23" s="20">
+      <c r="O23" s="20">
         <v>144</v>
       </c>
-      <c r="O23" s="24"/>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>
-      <c r="R23" s="20">
+      <c r="R23" s="24"/>
+      <c r="S23" s="20">
         <f t="shared" si="2"/>
         <v>864</v>
       </c>
-      <c r="S23" s="27">
+      <c r="T23" s="27">
         <v>516</v>
       </c>
-      <c r="T23" s="9" t="s">
+      <c r="U23" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U23" s="9"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20" t="str">
+      <c r="V23" s="9"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X23" s="20" t="str">
+      <c r="Y23" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y23" s="10" t="s">
+      <c r="Z23" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="29">
+    <row r="24" spans="1:26" ht="26.4">
       <c r="A24" s="6" t="s">
         <v>78</v>
       </c>
@@ -2732,52 +2860,55 @@
       <c r="H24" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="M24" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M24" s="9">
+      <c r="N24" s="9">
         <v>4</v>
       </c>
-      <c r="N24" s="20">
+      <c r="O24" s="20">
         <v>144</v>
       </c>
-      <c r="O24" s="24"/>
       <c r="P24" s="24"/>
       <c r="Q24" s="24"/>
-      <c r="R24" s="20">
+      <c r="R24" s="24"/>
+      <c r="S24" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S24" s="27">
+      <c r="T24" s="27">
         <v>458</v>
       </c>
-      <c r="T24" s="9" t="s">
+      <c r="U24" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U24" s="9"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20" t="str">
+      <c r="V24" s="9"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X24" s="20" t="str">
+      <c r="Y24" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y24" s="10" t="s">
+      <c r="Z24" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="29">
+    <row r="25" spans="1:26" ht="26.4">
       <c r="A25" s="6" t="s">
         <v>78</v>
       </c>
@@ -2803,52 +2934,55 @@
       <c r="H25" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="K25" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="L25" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="M25" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M25" s="9">
+      <c r="N25" s="9">
         <v>4</v>
       </c>
-      <c r="N25" s="20">
+      <c r="O25" s="20">
         <v>144</v>
       </c>
-      <c r="O25" s="24"/>
       <c r="P25" s="24"/>
       <c r="Q25" s="24"/>
-      <c r="R25" s="20">
+      <c r="R25" s="24"/>
+      <c r="S25" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S25" s="27">
+      <c r="T25" s="27">
         <v>422</v>
       </c>
-      <c r="T25" s="9" t="s">
+      <c r="U25" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U25" s="9"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20" t="str">
+      <c r="V25" s="9"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X25" s="20" t="str">
+      <c r="Y25" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y25" s="10" t="s">
+      <c r="Z25" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="29">
+    <row r="26" spans="1:26" ht="26.4">
       <c r="A26" s="6" t="s">
         <v>78</v>
       </c>
@@ -2874,52 +3008,55 @@
       <c r="H26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="K26" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="L26" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="M26" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M26" s="9">
+      <c r="N26" s="9">
         <v>8</v>
       </c>
-      <c r="N26" s="20">
+      <c r="O26" s="20">
         <v>144</v>
       </c>
-      <c r="O26" s="24"/>
       <c r="P26" s="24"/>
       <c r="Q26" s="24"/>
-      <c r="R26" s="20">
+      <c r="R26" s="24"/>
+      <c r="S26" s="20">
         <f t="shared" si="2"/>
         <v>1152</v>
       </c>
-      <c r="S26" s="27">
+      <c r="T26" s="27">
         <v>455</v>
       </c>
-      <c r="T26" s="9" t="s">
+      <c r="U26" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U26" s="9"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20" t="str">
+      <c r="V26" s="9"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X26" s="20" t="str">
+      <c r="Y26" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y26" s="10" t="s">
+      <c r="Z26" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="29">
+    <row r="27" spans="1:26" ht="27.6">
       <c r="A27" s="6" t="s">
         <v>78</v>
       </c>
@@ -2945,52 +3082,55 @@
       <c r="H27" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="L27" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="M27" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M27" s="9">
+      <c r="N27" s="9">
         <v>8</v>
       </c>
-      <c r="N27" s="20">
+      <c r="O27" s="20">
         <v>72</v>
       </c>
-      <c r="O27" s="24"/>
       <c r="P27" s="24"/>
       <c r="Q27" s="24"/>
-      <c r="R27" s="20">
+      <c r="R27" s="24"/>
+      <c r="S27" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S27" s="27">
+      <c r="T27" s="27">
         <v>133</v>
       </c>
-      <c r="T27" s="9" t="s">
+      <c r="U27" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U27" s="9"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20" t="str">
+      <c r="V27" s="9"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X27" s="20" t="str">
+      <c r="Y27" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y27" s="10" t="s">
+      <c r="Z27" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="29">
+    <row r="28" spans="1:26" ht="26.4">
       <c r="A28" s="6" t="s">
         <v>78</v>
       </c>
@@ -3016,52 +3156,55 @@
       <c r="H28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="K28" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="L28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="M28" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M28" s="9">
+      <c r="N28" s="9">
         <v>8</v>
       </c>
-      <c r="N28" s="20">
+      <c r="O28" s="20">
         <v>144</v>
       </c>
-      <c r="O28" s="24"/>
       <c r="P28" s="24"/>
       <c r="Q28" s="24"/>
-      <c r="R28" s="20">
+      <c r="R28" s="24"/>
+      <c r="S28" s="20">
         <f t="shared" si="2"/>
         <v>1152</v>
       </c>
-      <c r="S28" s="27">
+      <c r="T28" s="27">
         <v>435</v>
       </c>
-      <c r="T28" s="9" t="s">
+      <c r="U28" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U28" s="9"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20" t="str">
+      <c r="V28" s="9"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X28" s="20" t="str">
+      <c r="Y28" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y28" s="10" t="s">
+      <c r="Z28" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="29">
+    <row r="29" spans="1:26" ht="27.6">
       <c r="A29" s="6" t="s">
         <v>78</v>
       </c>
@@ -3087,52 +3230,55 @@
       <c r="H29" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="K29" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="L29" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="M29" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M29" s="9">
+      <c r="N29" s="9">
         <v>1</v>
       </c>
-      <c r="N29" s="20">
+      <c r="O29" s="20">
         <v>72</v>
       </c>
-      <c r="O29" s="24"/>
       <c r="P29" s="24"/>
       <c r="Q29" s="24"/>
-      <c r="R29" s="20">
+      <c r="R29" s="24"/>
+      <c r="S29" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S29" s="27">
+      <c r="T29" s="27">
         <v>118</v>
       </c>
-      <c r="T29" s="9" t="s">
+      <c r="U29" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U29" s="9"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20" t="str">
+      <c r="V29" s="9"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X29" s="20" t="str">
+      <c r="Y29" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y29" s="10" t="s">
+      <c r="Z29" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="29">
+    <row r="30" spans="1:26" ht="26.4">
       <c r="A30" s="6" t="s">
         <v>78</v>
       </c>
@@ -3158,52 +3304,55 @@
       <c r="H30" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="L30" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="M30" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M30" s="9">
+      <c r="N30" s="9">
         <v>4</v>
       </c>
-      <c r="N30" s="20">
+      <c r="O30" s="20">
         <v>144</v>
       </c>
-      <c r="O30" s="24"/>
       <c r="P30" s="24"/>
       <c r="Q30" s="24"/>
-      <c r="R30" s="20">
+      <c r="R30" s="24"/>
+      <c r="S30" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S30" s="27">
+      <c r="T30" s="27">
         <v>416</v>
       </c>
-      <c r="T30" s="9" t="s">
+      <c r="U30" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U30" s="9"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20" t="str">
+      <c r="V30" s="9"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X30" s="20" t="str">
+      <c r="Y30" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y30" s="10" t="s">
+      <c r="Z30" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="29">
+    <row r="31" spans="1:26" ht="26.4">
       <c r="A31" s="6" t="s">
         <v>78</v>
       </c>
@@ -3229,52 +3378,55 @@
       <c r="H31" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="L31" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="M31" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M31" s="9">
+      <c r="N31" s="9">
         <v>4</v>
       </c>
-      <c r="N31" s="20">
+      <c r="O31" s="20">
         <v>144</v>
       </c>
-      <c r="O31" s="24"/>
       <c r="P31" s="24"/>
       <c r="Q31" s="24"/>
-      <c r="R31" s="20">
+      <c r="R31" s="24"/>
+      <c r="S31" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S31" s="27">
+      <c r="T31" s="27">
         <v>419</v>
       </c>
-      <c r="T31" s="9" t="s">
+      <c r="U31" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20" t="str">
+      <c r="V31" s="9"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X31" s="20" t="str">
+      <c r="Y31" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y31" s="10" t="s">
+      <c r="Z31" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="29">
+    <row r="32" spans="1:26" ht="26.4">
       <c r="A32" s="6" t="s">
         <v>78</v>
       </c>
@@ -3300,52 +3452,55 @@
       <c r="H32" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="K32" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="L32" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="M32" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M32" s="9">
+      <c r="N32" s="9">
         <v>4</v>
       </c>
-      <c r="N32" s="20">
+      <c r="O32" s="20">
         <v>144</v>
       </c>
-      <c r="O32" s="24"/>
       <c r="P32" s="24"/>
       <c r="Q32" s="24"/>
-      <c r="R32" s="20">
+      <c r="R32" s="24"/>
+      <c r="S32" s="20">
         <f t="shared" si="2"/>
         <v>576</v>
       </c>
-      <c r="S32" s="27">
+      <c r="T32" s="27">
         <v>400</v>
       </c>
-      <c r="T32" s="9" t="s">
+      <c r="U32" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U32" s="9"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20" t="str">
+      <c r="V32" s="9"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X32" s="20" t="str">
+      <c r="Y32" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y32" s="10" t="s">
+      <c r="Z32" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="29">
+    <row r="33" spans="1:26" ht="26.4">
       <c r="A33" s="6" t="s">
         <v>78</v>
       </c>
@@ -3371,52 +3526,55 @@
       <c r="H33" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="L33" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="M33" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M33" s="9">
+      <c r="N33" s="9">
         <v>1</v>
       </c>
-      <c r="N33" s="20">
+      <c r="O33" s="20">
         <v>72</v>
       </c>
-      <c r="O33" s="24"/>
       <c r="P33" s="24"/>
       <c r="Q33" s="24"/>
-      <c r="R33" s="20">
+      <c r="R33" s="24"/>
+      <c r="S33" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S33" s="27">
+      <c r="T33" s="27">
         <v>140</v>
       </c>
-      <c r="T33" s="9" t="s">
+      <c r="U33" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U33" s="9"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20" t="str">
+      <c r="V33" s="9"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X33" s="20" t="str">
+      <c r="Y33" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y33" s="10" t="s">
+      <c r="Z33" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="29">
+    <row r="34" spans="1:26" ht="26.4">
       <c r="A34" s="6" t="s">
         <v>78</v>
       </c>
@@ -3442,52 +3600,55 @@
       <c r="H34" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="K34" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="L34" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="M34" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M34" s="9">
+      <c r="N34" s="9">
         <v>1</v>
       </c>
-      <c r="N34" s="20">
+      <c r="O34" s="20">
         <v>72</v>
       </c>
-      <c r="O34" s="24"/>
       <c r="P34" s="24"/>
       <c r="Q34" s="24"/>
-      <c r="R34" s="20">
+      <c r="R34" s="24"/>
+      <c r="S34" s="20">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="S34" s="27">
+      <c r="T34" s="27">
         <v>140</v>
       </c>
-      <c r="T34" s="9" t="s">
+      <c r="U34" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U34" s="9"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20" t="str">
+      <c r="V34" s="9"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X34" s="20" t="str">
+      <c r="Y34" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y34" s="10" t="s">
+      <c r="Z34" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="29">
+    <row r="35" spans="1:26" ht="26.4">
       <c r="A35" s="6" t="s">
         <v>78</v>
       </c>
@@ -3513,52 +3674,55 @@
       <c r="H35" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="K35" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K35" s="8" t="s">
+      <c r="L35" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="M35" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M35" s="9">
+      <c r="N35" s="9">
         <v>3</v>
       </c>
-      <c r="N35" s="20">
+      <c r="O35" s="20">
         <v>144</v>
       </c>
-      <c r="O35" s="24"/>
       <c r="P35" s="24"/>
       <c r="Q35" s="24"/>
-      <c r="R35" s="20">
+      <c r="R35" s="24"/>
+      <c r="S35" s="20">
         <f t="shared" si="2"/>
         <v>432</v>
       </c>
-      <c r="S35" s="27">
+      <c r="T35" s="27">
         <v>405</v>
       </c>
-      <c r="T35" s="9" t="s">
+      <c r="U35" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U35" s="9"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20" t="str">
+      <c r="V35" s="9"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X35" s="20" t="str">
+      <c r="Y35" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y35" s="10" t="s">
+      <c r="Z35" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="29">
+    <row r="36" spans="1:26" ht="26.4">
       <c r="A36" s="11" t="s">
         <v>78</v>
       </c>
@@ -3584,61 +3748,64 @@
       <c r="H36" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I36" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="J36" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="K36" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="K36" s="13" t="s">
+      <c r="L36" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="M36" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M36" s="14">
+      <c r="N36" s="14">
         <v>4</v>
       </c>
-      <c r="N36" s="21">
+      <c r="O36" s="21">
         <v>144</v>
       </c>
-      <c r="O36" s="24"/>
       <c r="P36" s="24"/>
       <c r="Q36" s="24"/>
-      <c r="R36" s="21">
-        <f>IF(OR(M36="",N36=""),"",M36*N36)</f>
+      <c r="R36" s="24"/>
+      <c r="S36" s="21">
+        <f>IF(OR(N36="",O36=""),"",N36*O36)</f>
         <v>576</v>
       </c>
-      <c r="S36" s="27">
+      <c r="T36" s="27">
         <v>392</v>
       </c>
-      <c r="T36" s="14" t="s">
+      <c r="U36" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="U36" s="14"/>
-      <c r="V36" s="21"/>
-      <c r="W36" s="21" t="str">
+      <c r="V36" s="14"/>
+      <c r="W36" s="21"/>
+      <c r="X36" s="21" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="X36" s="21" t="str">
+      <c r="Y36" s="21" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Y36" s="15" t="s">
+      <c r="Z36" s="15" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
-  <conditionalFormatting sqref="S4:S36">
+  <conditionalFormatting sqref="T4:T36">
     <cfRule type="expression" dxfId="5" priority="1">
-      <formula>$S4&lt;$F4</formula>
+      <formula>$T4&lt;$F4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="4" priority="2">
-      <formula>$S4&gt;=$F4</formula>
+      <formula>$T4&gt;=$F4</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3648,59 +3815,60 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:Z41"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="11" width="34" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
-    <col min="18" max="19" width="14" customWidth="1"/>
-    <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="22" width="12" customWidth="1"/>
-    <col min="23" max="24" width="14" customWidth="1"/>
-    <col min="25" max="25" width="16" customWidth="1"/>
+    <col min="8" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="34" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="15.69921875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
+    <col min="19" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="24" customWidth="1"/>
+    <col min="22" max="23" width="12" customWidth="1"/>
+    <col min="24" max="25" width="14" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:26" ht="21">
+      <c r="A1" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-    </row>
-    <row r="2" spans="1:25" ht="48">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
+    </row>
+    <row r="2" spans="1:26" ht="41.4">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -3725,59 +3893,62 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="O2" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="T2" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Y2" s="5" t="s">
+      <c r="Z2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="29">
+    <row r="3" spans="1:26" ht="26.4">
       <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
@@ -3803,60 +3974,63 @@
       <c r="H3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M3" s="9">
+      <c r="N3" s="9">
         <v>1</v>
       </c>
-      <c r="N3" s="20">
-        <f>2*36*M3</f>
+      <c r="O3" s="20">
+        <f>2*36*N3</f>
         <v>72</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="P3" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P3" s="24">
-        <v>0</v>
-      </c>
       <c r="Q3" s="24">
-        <f>4*36*P3</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="20">
-        <f>N3+Q3</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="24">
+        <f>4*36*Q3</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="20">
+        <f>O3+R3</f>
         <v>72</v>
       </c>
-      <c r="S3" s="27" t="s">
+      <c r="T3" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="U3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U3" s="9"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20" t="str">
-        <f t="shared" ref="W3:W24" si="1">IF(OR(U3="",V3=""),"",U3*V3)</f>
-        <v/>
-      </c>
+      <c r="V3" s="9"/>
+      <c r="W3" s="20"/>
       <c r="X3" s="20" t="str">
-        <f t="shared" ref="X3:X24" si="2">IF(OR(R3="",W3=""),"",R3-W3)</f>
-        <v/>
-      </c>
-      <c r="Y3" s="10" t="s">
+        <f t="shared" ref="X3:X24" si="1">IF(OR(V3="",W3=""),"",V3*W3)</f>
+        <v/>
+      </c>
+      <c r="Y3" s="20" t="str">
+        <f t="shared" ref="Y3:Y24" si="2">IF(OR(S3="",X3=""),"",S3-X3)</f>
+        <v/>
+      </c>
+      <c r="Z3" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="29">
+    <row r="4" spans="1:26" ht="26.4">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -3882,60 +4056,63 @@
       <c r="H4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M4" s="9">
+      <c r="N4" s="9">
         <v>2</v>
       </c>
-      <c r="N4" s="20">
-        <f t="shared" ref="N4:N23" si="3">2*36*M4</f>
+      <c r="O4" s="20">
+        <f t="shared" ref="O4:O23" si="3">2*36*N4</f>
         <v>144</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="P4" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P4" s="24">
+      <c r="Q4" s="24">
         <v>5</v>
       </c>
-      <c r="Q4" s="24">
-        <f t="shared" ref="Q4:Q24" si="4">4*36*P4</f>
+      <c r="R4" s="24">
+        <f t="shared" ref="R4:R24" si="4">4*36*Q4</f>
         <v>720</v>
       </c>
-      <c r="R4" s="20">
-        <f t="shared" ref="R4:R23" si="5">N4+Q4</f>
+      <c r="S4" s="20">
+        <f t="shared" ref="S4:S23" si="5">O4+R4</f>
         <v>864</v>
       </c>
-      <c r="S4" s="27">
+      <c r="T4" s="27">
         <v>380</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20" t="str">
+      <c r="V4" s="9"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X4" s="20" t="str">
+      <c r="Y4" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y4" s="10" t="s">
+      <c r="Z4" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="29">
+    <row r="5" spans="1:26" ht="26.4">
       <c r="A5" s="6" t="s">
         <v>22</v>
       </c>
@@ -3961,60 +4138,63 @@
       <c r="H5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-      <c r="N5" s="20">
+      <c r="N5" s="9">
+        <v>0</v>
+      </c>
+      <c r="O5" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="P5" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P5" s="24">
+      <c r="Q5" s="24">
         <v>1</v>
       </c>
-      <c r="Q5" s="24">
+      <c r="R5" s="24">
         <f t="shared" si="4"/>
         <v>144</v>
       </c>
-      <c r="R5" s="20">
+      <c r="S5" s="20">
         <f t="shared" si="5"/>
         <v>144</v>
       </c>
-      <c r="S5" s="27">
+      <c r="T5" s="27">
         <v>325</v>
       </c>
-      <c r="T5" s="9" t="s">
+      <c r="U5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="9"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20" t="str">
+      <c r="V5" s="9"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X5" s="20" t="str">
+      <c r="Y5" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y5" s="10" t="s">
+      <c r="Z5" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="29">
+    <row r="6" spans="1:26" ht="26.4">
       <c r="A6" s="6" t="s">
         <v>22</v>
       </c>
@@ -4040,60 +4220,63 @@
       <c r="H6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="M6" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M6" s="9">
+      <c r="N6" s="9">
         <v>1</v>
       </c>
-      <c r="N6" s="20">
+      <c r="O6" s="20">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O6" s="25" t="s">
+      <c r="P6" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P6" s="24">
-        <v>0</v>
-      </c>
       <c r="Q6" s="24">
+        <v>0</v>
+      </c>
+      <c r="R6" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R6" s="20">
+      <c r="S6" s="20">
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S6" s="27">
+      <c r="T6" s="27">
         <v>205</v>
       </c>
-      <c r="T6" s="9" t="s">
+      <c r="U6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U6" s="9"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20" t="str">
+      <c r="V6" s="9"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X6" s="20" t="str">
+      <c r="Y6" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Z6" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="29">
+    <row r="7" spans="1:26" ht="26.4">
       <c r="A7" s="6" t="s">
         <v>22</v>
       </c>
@@ -4119,60 +4302,63 @@
       <c r="H7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="M7" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M7" s="9">
+      <c r="N7" s="9">
         <v>1</v>
       </c>
-      <c r="N7" s="20">
+      <c r="O7" s="20">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="P7" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P7" s="24">
-        <v>0</v>
-      </c>
       <c r="Q7" s="24">
+        <v>0</v>
+      </c>
+      <c r="R7" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R7" s="20">
+      <c r="S7" s="20">
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S7" s="27">
+      <c r="T7" s="27">
         <v>201</v>
       </c>
-      <c r="T7" s="9" t="s">
+      <c r="U7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U7" s="9"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20" t="str">
+      <c r="V7" s="9"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X7" s="20" t="str">
+      <c r="Y7" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y7" s="10" t="s">
+      <c r="Z7" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="29">
+    <row r="8" spans="1:26" ht="26.4">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
@@ -4198,60 +4384,63 @@
       <c r="H8" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M8" s="9">
+      <c r="N8" s="9">
         <v>1</v>
       </c>
-      <c r="N8" s="20">
+      <c r="O8" s="20">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O8" s="25" t="s">
+      <c r="P8" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P8" s="24">
-        <v>0</v>
-      </c>
       <c r="Q8" s="24">
+        <v>0</v>
+      </c>
+      <c r="R8" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R8" s="20">
+      <c r="S8" s="20">
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S8" s="27">
+      <c r="T8" s="27">
         <v>186</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U8" s="9"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20" t="str">
+      <c r="V8" s="9"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X8" s="20" t="str">
+      <c r="Y8" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y8" s="10" t="s">
+      <c r="Z8" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="29">
+    <row r="9" spans="1:26" ht="26.4">
       <c r="A9" s="6" t="s">
         <v>22</v>
       </c>
@@ -4277,60 +4466,63 @@
       <c r="H9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="K9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="L9" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M9" s="9">
+      <c r="N9" s="9">
         <v>1</v>
       </c>
-      <c r="N9" s="20">
+      <c r="O9" s="20">
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O9" s="25" t="s">
+      <c r="P9" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P9" s="24">
-        <v>0</v>
-      </c>
       <c r="Q9" s="24">
+        <v>0</v>
+      </c>
+      <c r="R9" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R9" s="20">
+      <c r="S9" s="20">
         <f t="shared" si="5"/>
         <v>72</v>
       </c>
-      <c r="S9" s="27">
+      <c r="T9" s="27">
         <v>187</v>
       </c>
-      <c r="T9" s="9" t="s">
+      <c r="U9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U9" s="9"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20" t="str">
+      <c r="V9" s="9"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X9" s="20" t="str">
+      <c r="Y9" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y9" s="10" t="s">
+      <c r="Z9" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="29">
+    <row r="10" spans="1:26" ht="26.4">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -4356,60 +4548,63 @@
       <c r="H10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="L10" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="20">
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O10" s="25" t="s">
+      <c r="P10" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P10" s="24">
+      <c r="Q10" s="24">
         <v>4</v>
       </c>
-      <c r="Q10" s="24">
+      <c r="R10" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
-      <c r="R10" s="20">
+      <c r="S10" s="20">
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S10" s="27">
+      <c r="T10" s="27">
         <v>753</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="U10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U10" s="9"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20" t="str">
+      <c r="V10" s="9"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X10" s="20" t="str">
+      <c r="Y10" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y10" s="10" t="s">
+      <c r="Z10" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="29">
+    <row r="11" spans="1:26" ht="26.4">
       <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
@@ -4435,60 +4630,63 @@
       <c r="H11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="K11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="L11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="M11" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M11" s="9">
-        <v>0</v>
-      </c>
-      <c r="N11" s="20">
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O11" s="25" t="s">
+      <c r="P11" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P11" s="24">
+      <c r="Q11" s="24">
         <v>2</v>
       </c>
-      <c r="Q11" s="24">
+      <c r="R11" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
-      <c r="R11" s="20">
-        <f>N11+Q11</f>
+      <c r="S11" s="20">
+        <f>O11+R11</f>
         <v>288</v>
       </c>
-      <c r="S11" s="27">
+      <c r="T11" s="27">
         <v>801</v>
       </c>
-      <c r="T11" s="9" t="s">
+      <c r="U11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U11" s="9"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20" t="str">
-        <f t="shared" ref="W11" si="7">IF(OR(U11="",V11=""),"",U11*V11)</f>
-        <v/>
-      </c>
+      <c r="V11" s="9"/>
+      <c r="W11" s="20"/>
       <c r="X11" s="20" t="str">
-        <f t="shared" ref="X11" si="8">IF(OR(R11="",W11=""),"",R11-W11)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="10" t="s">
+        <f t="shared" ref="X11" si="7">IF(OR(V11="",W11=""),"",V11*W11)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="20" t="str">
+        <f t="shared" ref="Y11" si="8">IF(OR(S11="",X11=""),"",S11-X11)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="29">
+    <row r="12" spans="1:26" ht="26.4">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
@@ -4514,60 +4712,63 @@
       <c r="H12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="M12" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-      <c r="N12" s="20">
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="P12" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P12" s="24">
+      <c r="Q12" s="24">
         <v>6</v>
       </c>
-      <c r="Q12" s="24">
+      <c r="R12" s="24">
         <f t="shared" si="4"/>
         <v>864</v>
       </c>
-      <c r="R12" s="20">
+      <c r="S12" s="20">
         <f t="shared" si="5"/>
         <v>864</v>
       </c>
-      <c r="S12" s="27">
+      <c r="T12" s="27">
         <v>1107</v>
       </c>
-      <c r="T12" s="9" t="s">
+      <c r="U12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U12" s="9"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="20" t="str">
+      <c r="V12" s="9"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X12" s="20" t="str">
+      <c r="Y12" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y12" s="10" t="s">
+      <c r="Z12" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="29">
+    <row r="13" spans="1:26" ht="26.4">
       <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
@@ -4593,60 +4794,63 @@
       <c r="H13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="K13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="L13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="M13" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M13" s="9">
-        <v>0</v>
-      </c>
-      <c r="N13" s="20">
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O13" s="25" t="s">
+      <c r="P13" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P13" s="24">
+      <c r="Q13" s="24">
         <v>2</v>
       </c>
-      <c r="Q13" s="24">
+      <c r="R13" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
-      <c r="R13" s="20">
+      <c r="S13" s="20">
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S13" s="27">
+      <c r="T13" s="27">
         <v>740</v>
       </c>
-      <c r="T13" s="9" t="s">
+      <c r="U13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="20" t="str">
+      <c r="V13" s="9"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X13" s="20" t="str">
+      <c r="Y13" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y13" s="10" t="s">
+      <c r="Z13" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="29">
+    <row r="14" spans="1:26" ht="26.4">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
@@ -4672,60 +4876,63 @@
       <c r="H14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="M14" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-      <c r="N14" s="20">
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O14" s="25" t="s">
+      <c r="P14" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P14" s="24">
+      <c r="Q14" s="24">
         <v>3</v>
       </c>
-      <c r="Q14" s="24">
+      <c r="R14" s="24">
         <f t="shared" si="4"/>
         <v>432</v>
       </c>
-      <c r="R14" s="20">
+      <c r="S14" s="20">
         <f t="shared" si="5"/>
         <v>432</v>
       </c>
-      <c r="S14" s="27">
+      <c r="T14" s="27">
         <v>865</v>
       </c>
-      <c r="T14" s="9" t="s">
+      <c r="U14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U14" s="9"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20" t="str">
+      <c r="V14" s="9"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X14" s="20" t="str">
+      <c r="Y14" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y14" s="10" t="s">
+      <c r="Z14" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="29">
+    <row r="15" spans="1:26" ht="26.4">
       <c r="A15" s="6" t="s">
         <v>22</v>
       </c>
@@ -4751,60 +4958,63 @@
       <c r="H15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="L15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="M15" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M15" s="9">
-        <v>0</v>
-      </c>
-      <c r="N15" s="20">
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O15" s="25" t="s">
+      <c r="P15" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P15" s="24">
+      <c r="Q15" s="24">
         <v>2</v>
       </c>
-      <c r="Q15" s="24">
+      <c r="R15" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
-      <c r="R15" s="20">
+      <c r="S15" s="20">
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S15" s="27">
+      <c r="T15" s="27">
         <v>403</v>
       </c>
-      <c r="T15" s="9" t="s">
+      <c r="U15" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U15" s="9"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20" t="str">
+      <c r="V15" s="9"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X15" s="20" t="str">
+      <c r="Y15" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y15" s="10" t="s">
+      <c r="Z15" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="29">
+    <row r="16" spans="1:26" ht="26.4">
       <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
@@ -4830,60 +5040,63 @@
       <c r="H16" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="L16" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="20">
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O16" s="25" t="s">
+      <c r="P16" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P16" s="24">
+      <c r="Q16" s="24">
         <v>1</v>
       </c>
-      <c r="Q16" s="24">
+      <c r="R16" s="24">
         <f t="shared" si="4"/>
         <v>144</v>
       </c>
-      <c r="R16" s="20">
+      <c r="S16" s="20">
         <f t="shared" si="5"/>
         <v>144</v>
       </c>
-      <c r="S16" s="27">
+      <c r="T16" s="27">
         <v>403</v>
       </c>
-      <c r="T16" s="9" t="s">
+      <c r="U16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U16" s="9"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20" t="str">
+      <c r="V16" s="9"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X16" s="20" t="str">
+      <c r="Y16" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y16" s="10" t="s">
+      <c r="Z16" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="29">
+    <row r="17" spans="1:26" ht="26.4">
       <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
@@ -4909,60 +5122,63 @@
       <c r="H17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="L17" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="M17" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M17" s="9">
-        <v>0</v>
-      </c>
-      <c r="N17" s="20">
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O17" s="25" t="s">
+      <c r="P17" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P17" s="24">
+      <c r="Q17" s="24">
         <v>4</v>
       </c>
-      <c r="Q17" s="24">
+      <c r="R17" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
-      <c r="R17" s="20">
+      <c r="S17" s="20">
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S17" s="27">
+      <c r="T17" s="27">
         <v>1069</v>
       </c>
-      <c r="T17" s="9" t="s">
+      <c r="U17" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U17" s="9"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20" t="str">
+      <c r="V17" s="9"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X17" s="20" t="str">
+      <c r="Y17" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y17" s="10" t="s">
+      <c r="Z17" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="29">
+    <row r="18" spans="1:26" ht="26.4">
       <c r="A18" s="6" t="s">
         <v>22</v>
       </c>
@@ -4988,60 +5204,63 @@
       <c r="H18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="L18" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="M18" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="20">
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O18" s="25" t="s">
+      <c r="P18" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P18" s="24">
+      <c r="Q18" s="24">
         <v>2</v>
       </c>
-      <c r="Q18" s="24">
+      <c r="R18" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
-      <c r="R18" s="20">
+      <c r="S18" s="20">
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S18" s="27">
+      <c r="T18" s="27">
         <v>854</v>
       </c>
-      <c r="T18" s="9" t="s">
+      <c r="U18" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U18" s="9"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20" t="str">
+      <c r="V18" s="9"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X18" s="20" t="str">
+      <c r="Y18" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y18" s="10" t="s">
+      <c r="Z18" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="29">
+    <row r="19" spans="1:26" ht="26.4">
       <c r="A19" s="6" t="s">
         <v>22</v>
       </c>
@@ -5067,60 +5286,63 @@
       <c r="H19" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="M19" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M19" s="9">
-        <v>0</v>
-      </c>
-      <c r="N19" s="20">
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O19" s="25" t="s">
+      <c r="P19" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P19" s="24">
+      <c r="Q19" s="24">
         <v>6</v>
       </c>
-      <c r="Q19" s="24">
+      <c r="R19" s="24">
         <f t="shared" si="4"/>
         <v>864</v>
       </c>
-      <c r="R19" s="20">
+      <c r="S19" s="20">
         <f t="shared" si="5"/>
         <v>864</v>
       </c>
-      <c r="S19" s="27">
+      <c r="T19" s="27">
         <v>538</v>
       </c>
-      <c r="T19" s="9" t="s">
+      <c r="U19" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U19" s="9"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20" t="str">
+      <c r="V19" s="9"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X19" s="20" t="str">
+      <c r="Y19" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y19" s="10" t="s">
+      <c r="Z19" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="29">
+    <row r="20" spans="1:26" ht="26.4">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
@@ -5146,60 +5368,63 @@
       <c r="H20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="L20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="M20" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M20" s="9">
-        <v>0</v>
-      </c>
-      <c r="N20" s="20">
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+      <c r="O20" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O20" s="25" t="s">
+      <c r="P20" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P20" s="24">
+      <c r="Q20" s="24">
         <v>4</v>
       </c>
-      <c r="Q20" s="24">
+      <c r="R20" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
-      <c r="R20" s="20">
+      <c r="S20" s="20">
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S20" s="27">
+      <c r="T20" s="27">
         <v>1064</v>
       </c>
-      <c r="T20" s="9" t="s">
+      <c r="U20" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U20" s="9"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20" t="str">
+      <c r="V20" s="9"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X20" s="20" t="str">
+      <c r="Y20" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y20" s="10" t="s">
+      <c r="Z20" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="29">
+    <row r="21" spans="1:26" ht="26.4">
       <c r="A21" s="6" t="s">
         <v>22</v>
       </c>
@@ -5225,60 +5450,63 @@
       <c r="H21" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="M21" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M21" s="9">
-        <v>0</v>
-      </c>
-      <c r="N21" s="20">
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O21" s="25" t="s">
+      <c r="P21" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P21" s="24">
+      <c r="Q21" s="24">
         <v>1</v>
       </c>
-      <c r="Q21" s="24">
+      <c r="R21" s="24">
         <f t="shared" si="4"/>
         <v>144</v>
       </c>
-      <c r="R21" s="20">
+      <c r="S21" s="20">
         <f t="shared" si="5"/>
         <v>144</v>
       </c>
-      <c r="S21" s="27">
+      <c r="T21" s="27">
         <v>538</v>
       </c>
-      <c r="T21" s="9" t="s">
+      <c r="U21" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U21" s="9"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20" t="str">
+      <c r="V21" s="9"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X21" s="20" t="str">
+      <c r="Y21" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y21" s="10" t="s">
+      <c r="Z21" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="29">
+    <row r="22" spans="1:26" ht="26.4">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -5304,60 +5532,63 @@
       <c r="H22" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="L22" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M22" s="9">
-        <v>0</v>
-      </c>
-      <c r="N22" s="20">
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+      <c r="O22" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O22" s="25" t="s">
+      <c r="P22" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P22" s="24">
+      <c r="Q22" s="24">
         <v>4</v>
       </c>
-      <c r="Q22" s="24">
+      <c r="R22" s="24">
         <f t="shared" si="4"/>
         <v>576</v>
       </c>
-      <c r="R22" s="20">
+      <c r="S22" s="20">
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
-      <c r="S22" s="27">
+      <c r="T22" s="27">
         <v>1133</v>
       </c>
-      <c r="T22" s="9" t="s">
+      <c r="U22" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U22" s="9"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20" t="str">
+      <c r="V22" s="9"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X22" s="20" t="str">
+      <c r="Y22" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y22" s="10" t="s">
+      <c r="Z22" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="29">
+    <row r="23" spans="1:26" ht="26.4">
       <c r="A23" s="6" t="s">
         <v>22</v>
       </c>
@@ -5383,60 +5614,63 @@
       <c r="H23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="M23" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M23" s="9">
-        <v>0</v>
-      </c>
-      <c r="N23" s="20">
+      <c r="N23" s="9">
+        <v>0</v>
+      </c>
+      <c r="O23" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O23" s="25" t="s">
+      <c r="P23" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P23" s="24">
+      <c r="Q23" s="24">
         <v>2</v>
       </c>
-      <c r="Q23" s="24">
+      <c r="R23" s="24">
         <f t="shared" si="4"/>
         <v>288</v>
       </c>
-      <c r="R23" s="20">
+      <c r="S23" s="20">
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
-      <c r="S23" s="27">
+      <c r="T23" s="27">
         <v>900</v>
       </c>
-      <c r="T23" s="9" t="s">
+      <c r="U23" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U23" s="9"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20" t="str">
+      <c r="V23" s="9"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X23" s="20" t="str">
+      <c r="Y23" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y23" s="10" t="s">
+      <c r="Z23" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="29">
+    <row r="24" spans="1:26" ht="26.4">
       <c r="A24" s="6" t="s">
         <v>78</v>
       </c>
@@ -5462,64 +5696,67 @@
       <c r="H24" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="M24" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M24" s="9">
+      <c r="N24" s="9">
         <v>1</v>
       </c>
-      <c r="N24" s="20">
-        <f>72*M24</f>
+      <c r="O24" s="20">
+        <f>72*N24</f>
         <v>72</v>
       </c>
-      <c r="O24" s="25" t="s">
+      <c r="P24" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P24" s="24">
-        <v>0</v>
-      </c>
       <c r="Q24" s="24">
+        <v>0</v>
+      </c>
+      <c r="R24" s="24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R24" s="20">
-        <f>N24</f>
+      <c r="S24" s="20">
+        <f>O24</f>
         <v>72</v>
       </c>
-      <c r="S24" s="33">
+      <c r="T24" s="29">
         <v>229</v>
       </c>
-      <c r="T24" s="9" t="s">
+      <c r="U24" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U24" s="9"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20" t="str">
+      <c r="V24" s="9"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="X24" s="20" t="str">
+      <c r="Y24" s="20" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Y24" s="10" t="s">
+      <c r="Z24" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="29">
+    <row r="25" spans="1:26" ht="26.4">
       <c r="A25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="28">
         <v>202</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -5541,60 +5778,63 @@
       <c r="H25" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="K25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="L25" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="M25" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M25" s="9">
+      <c r="N25" s="9">
         <v>2</v>
       </c>
-      <c r="N25" s="20">
-        <f t="shared" ref="N25:N38" si="10">72*M25</f>
+      <c r="O25" s="20">
+        <f t="shared" ref="O25:O38" si="10">72*N25</f>
         <v>144</v>
       </c>
-      <c r="O25" s="25" t="s">
+      <c r="P25" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P25" s="24">
-        <v>0</v>
-      </c>
       <c r="Q25" s="24">
-        <f t="shared" ref="Q25:Q34" si="11">4*36*P25</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="20">
-        <f t="shared" ref="R25:R38" si="12">N25</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="24">
+        <f t="shared" ref="R25:R33" si="11">4*36*Q25</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="20">
+        <f t="shared" ref="S25:S38" si="12">O25</f>
         <v>144</v>
       </c>
-      <c r="S25" s="33">
+      <c r="T25" s="29">
         <v>168</v>
       </c>
-      <c r="T25" s="9" t="s">
+      <c r="U25" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U25" s="9"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20" t="str">
-        <f t="shared" ref="W25" si="13">IF(OR(U25="",V25=""),"",U25*V25)</f>
-        <v/>
-      </c>
+      <c r="V25" s="9"/>
+      <c r="W25" s="20"/>
       <c r="X25" s="20" t="str">
-        <f t="shared" ref="X25" si="14">IF(OR(R25="",W25=""),"",R25-W25)</f>
-        <v/>
-      </c>
-      <c r="Y25" s="10" t="s">
+        <f t="shared" ref="X25" si="13">IF(OR(V25="",W25=""),"",V25*W25)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="20" t="str">
+        <f t="shared" ref="Y25" si="14">IF(OR(S25="",X25=""),"",S25-X25)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="29">
+    <row r="26" spans="1:26" ht="26.4">
       <c r="A26" s="6" t="s">
         <v>78</v>
       </c>
@@ -5614,66 +5854,69 @@
         <v>80</v>
       </c>
       <c r="G26" s="18">
-        <f>ROUND(F26/0.8,0)</f>
+        <f t="shared" ref="G26:G38" si="15">ROUND(F26/0.8,0)</f>
         <v>100</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="K26" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="L26" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="M26" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M26" s="9">
-        <v>0</v>
-      </c>
-      <c r="N26" s="20">
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+      <c r="O26" s="20">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="O26" s="25" t="s">
+      <c r="P26" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P26" s="24">
-        <v>0</v>
-      </c>
       <c r="Q26" s="24">
+        <v>0</v>
+      </c>
+      <c r="R26" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R26" s="20">
+      <c r="S26" s="20">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S26" s="33">
-        <v>0</v>
-      </c>
-      <c r="T26" s="9" t="s">
+      <c r="T26" s="29">
+        <v>0</v>
+      </c>
+      <c r="U26" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U26" s="9"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20" t="str">
-        <f>IF(OR(U26="",V26=""),"",U26*V26)</f>
-        <v/>
-      </c>
+      <c r="V26" s="9"/>
+      <c r="W26" s="20"/>
       <c r="X26" s="20" t="str">
-        <f>IF(OR(R26="",W26=""),"",R26-W26)</f>
-        <v/>
-      </c>
-      <c r="Y26" s="10" t="s">
+        <f t="shared" ref="X26:X38" si="16">IF(OR(V26="",W26=""),"",V26*W26)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="20" t="str">
+        <f t="shared" ref="Y26:Y38" si="17">IF(OR(S26="",X26=""),"",S26-X26)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="29">
+    <row r="27" spans="1:26" ht="26.4">
       <c r="A27" s="6" t="s">
         <v>78</v>
       </c>
@@ -5693,66 +5936,69 @@
         <v>320</v>
       </c>
       <c r="G27" s="18">
-        <f>ROUND(F27/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="L27" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="M27" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M27" s="9">
+      <c r="N27" s="9">
         <v>4</v>
       </c>
-      <c r="N27" s="20">
-        <f>72*M27</f>
+      <c r="O27" s="20">
+        <f>72*N27</f>
         <v>288</v>
       </c>
-      <c r="O27" s="25" t="s">
+      <c r="P27" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P27" s="24">
-        <v>0</v>
-      </c>
       <c r="Q27" s="24">
+        <v>0</v>
+      </c>
+      <c r="R27" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R27" s="20">
+      <c r="S27" s="20">
         <f t="shared" si="12"/>
         <v>288</v>
       </c>
-      <c r="S27" s="33">
+      <c r="T27" s="29">
         <v>291</v>
       </c>
-      <c r="T27" s="9" t="s">
+      <c r="U27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U27" s="9"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20" t="str">
-        <f>IF(OR(U27="",V27=""),"",U27*V27)</f>
-        <v/>
-      </c>
+      <c r="V27" s="9"/>
+      <c r="W27" s="20"/>
       <c r="X27" s="20" t="str">
-        <f>IF(OR(R27="",W27=""),"",R27-W27)</f>
-        <v/>
-      </c>
-      <c r="Y27" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y27" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z27" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="29">
+    <row r="28" spans="1:26" ht="26.4">
       <c r="A28" s="6" t="s">
         <v>78</v>
       </c>
@@ -5772,66 +6018,69 @@
         <v>320</v>
       </c>
       <c r="G28" s="18">
-        <f>ROUND(F28/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="K28" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="L28" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="M28" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M28" s="9">
+      <c r="N28" s="9">
         <v>4</v>
       </c>
-      <c r="N28" s="20">
+      <c r="O28" s="20">
         <f t="shared" si="10"/>
         <v>288</v>
       </c>
-      <c r="O28" s="25" t="s">
+      <c r="P28" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P28" s="24">
-        <v>0</v>
-      </c>
       <c r="Q28" s="24">
+        <v>0</v>
+      </c>
+      <c r="R28" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R28" s="20">
+      <c r="S28" s="20">
         <f t="shared" si="12"/>
         <v>288</v>
       </c>
-      <c r="S28" s="33">
+      <c r="T28" s="29">
         <v>384</v>
       </c>
-      <c r="T28" s="9" t="s">
+      <c r="U28" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U28" s="9"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20" t="str">
-        <f>IF(OR(U28="",V28=""),"",U28*V28)</f>
-        <v/>
-      </c>
+      <c r="V28" s="9"/>
+      <c r="W28" s="20"/>
       <c r="X28" s="20" t="str">
-        <f>IF(OR(R28="",W28=""),"",R28-W28)</f>
-        <v/>
-      </c>
-      <c r="Y28" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y28" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z28" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="29">
+    <row r="29" spans="1:26" ht="26.4">
       <c r="A29" s="6" t="s">
         <v>78</v>
       </c>
@@ -5851,66 +6100,69 @@
         <v>320</v>
       </c>
       <c r="G29" s="18">
-        <f>ROUND(F29/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J29" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="K29" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="L29" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="M29" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M29" s="9">
+      <c r="N29" s="9">
         <v>5</v>
       </c>
-      <c r="N29" s="20">
+      <c r="O29" s="20">
         <f t="shared" si="10"/>
         <v>360</v>
       </c>
-      <c r="O29" s="25" t="s">
+      <c r="P29" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P29" s="24">
-        <v>0</v>
-      </c>
       <c r="Q29" s="24">
+        <v>0</v>
+      </c>
+      <c r="R29" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R29" s="20">
+      <c r="S29" s="20">
         <f t="shared" si="12"/>
         <v>360</v>
       </c>
-      <c r="S29" s="33">
+      <c r="T29" s="29">
         <v>375</v>
       </c>
-      <c r="T29" s="9" t="s">
+      <c r="U29" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U29" s="9"/>
-      <c r="V29" s="20"/>
-      <c r="W29" s="20" t="str">
-        <f>IF(OR(U29="",V29=""),"",U29*V29)</f>
-        <v/>
-      </c>
+      <c r="V29" s="9"/>
+      <c r="W29" s="20"/>
       <c r="X29" s="20" t="str">
-        <f>IF(OR(R29="",W29=""),"",R29-W29)</f>
-        <v/>
-      </c>
-      <c r="Y29" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y29" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z29" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="29">
+    <row r="30" spans="1:26" ht="26.4">
       <c r="A30" s="6" t="s">
         <v>78</v>
       </c>
@@ -5930,66 +6182,69 @@
         <v>160</v>
       </c>
       <c r="G30" s="18">
-        <f>ROUND(F30/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>200</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="L30" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="M30" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M30" s="9">
+      <c r="N30" s="9">
         <v>7</v>
       </c>
-      <c r="N30" s="20">
+      <c r="O30" s="20">
         <f t="shared" si="10"/>
         <v>504</v>
       </c>
-      <c r="O30" s="25" t="s">
+      <c r="P30" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P30" s="24">
-        <v>0</v>
-      </c>
       <c r="Q30" s="24">
+        <v>0</v>
+      </c>
+      <c r="R30" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R30" s="20">
+      <c r="S30" s="20">
         <f t="shared" si="12"/>
         <v>504</v>
       </c>
-      <c r="S30" s="33">
+      <c r="T30" s="29">
         <v>316</v>
       </c>
-      <c r="T30" s="9" t="s">
+      <c r="U30" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U30" s="9"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20" t="str">
-        <f>IF(OR(U30="",V30=""),"",U30*V30)</f>
-        <v/>
-      </c>
+      <c r="V30" s="9"/>
+      <c r="W30" s="20"/>
       <c r="X30" s="20" t="str">
-        <f>IF(OR(R30="",W30=""),"",R30-W30)</f>
-        <v/>
-      </c>
-      <c r="Y30" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y30" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z30" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="29">
+    <row r="31" spans="1:26" ht="26.4">
       <c r="A31" s="6" t="s">
         <v>78</v>
       </c>
@@ -6009,66 +6264,69 @@
         <v>320</v>
       </c>
       <c r="G31" s="18">
-        <f>ROUND(F31/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="L31" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="M31" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M31" s="9">
+      <c r="N31" s="9">
         <v>9</v>
       </c>
-      <c r="N31" s="20">
+      <c r="O31" s="20">
         <f t="shared" si="10"/>
         <v>648</v>
       </c>
-      <c r="O31" s="25" t="s">
+      <c r="P31" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P31" s="24">
-        <v>0</v>
-      </c>
       <c r="Q31" s="24">
+        <v>0</v>
+      </c>
+      <c r="R31" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R31" s="20">
+      <c r="S31" s="20">
         <f t="shared" si="12"/>
         <v>648</v>
       </c>
-      <c r="S31" s="33">
+      <c r="T31" s="29">
         <v>476</v>
       </c>
-      <c r="T31" s="9" t="s">
+      <c r="U31" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="20"/>
-      <c r="W31" s="20" t="str">
-        <f>IF(OR(U31="",V31=""),"",U31*V31)</f>
-        <v/>
-      </c>
+      <c r="V31" s="9"/>
+      <c r="W31" s="20"/>
       <c r="X31" s="20" t="str">
-        <f>IF(OR(R31="",W31=""),"",R31-W31)</f>
-        <v/>
-      </c>
-      <c r="Y31" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y31" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z31" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="29">
+    <row r="32" spans="1:26" ht="26.4">
       <c r="A32" s="6" t="s">
         <v>78</v>
       </c>
@@ -6088,66 +6346,69 @@
         <v>320</v>
       </c>
       <c r="G32" s="18">
-        <f>ROUND(F32/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="K32" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="L32" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="M32" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M32" s="9">
+      <c r="N32" s="9">
         <v>6</v>
       </c>
-      <c r="N32" s="20">
+      <c r="O32" s="20">
         <f t="shared" si="10"/>
         <v>432</v>
       </c>
-      <c r="O32" s="25" t="s">
+      <c r="P32" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P32" s="24">
-        <v>0</v>
-      </c>
       <c r="Q32" s="24">
+        <v>0</v>
+      </c>
+      <c r="R32" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R32" s="20">
+      <c r="S32" s="20">
         <f t="shared" si="12"/>
         <v>432</v>
       </c>
-      <c r="S32" s="33">
+      <c r="T32" s="29">
         <v>552</v>
       </c>
-      <c r="T32" s="9" t="s">
+      <c r="U32" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U32" s="9"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20" t="str">
-        <f>IF(OR(U32="",V32=""),"",U32*V32)</f>
-        <v/>
-      </c>
+      <c r="V32" s="9"/>
+      <c r="W32" s="20"/>
       <c r="X32" s="20" t="str">
-        <f>IF(OR(R32="",W32=""),"",R32-W32)</f>
-        <v/>
-      </c>
-      <c r="Y32" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y32" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z32" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="29">
+    <row r="33" spans="1:26" ht="26.4">
       <c r="A33" s="6" t="s">
         <v>78</v>
       </c>
@@ -6167,66 +6428,69 @@
         <v>80</v>
       </c>
       <c r="G33" s="18">
-        <f>ROUND(F33/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>100</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="L33" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="M33" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M33" s="9">
+      <c r="N33" s="9">
         <v>2</v>
       </c>
-      <c r="N33" s="20">
+      <c r="O33" s="20">
         <f t="shared" si="10"/>
         <v>144</v>
       </c>
-      <c r="O33" s="25" t="s">
+      <c r="P33" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P33" s="24">
-        <v>0</v>
-      </c>
       <c r="Q33" s="24">
+        <v>0</v>
+      </c>
+      <c r="R33" s="24">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R33" s="20">
+      <c r="S33" s="20">
         <f t="shared" si="12"/>
         <v>144</v>
       </c>
-      <c r="S33" s="33">
+      <c r="T33" s="29">
         <v>227</v>
       </c>
-      <c r="T33" s="9" t="s">
+      <c r="U33" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U33" s="9"/>
-      <c r="V33" s="20"/>
-      <c r="W33" s="20" t="str">
-        <f>IF(OR(U33="",V33=""),"",U33*V33)</f>
-        <v/>
-      </c>
+      <c r="V33" s="9"/>
+      <c r="W33" s="20"/>
       <c r="X33" s="20" t="str">
-        <f>IF(OR(R33="",W33=""),"",R33-W33)</f>
-        <v/>
-      </c>
-      <c r="Y33" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y33" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z33" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="29">
+    <row r="34" spans="1:26" ht="26.4">
       <c r="A34" s="6" t="s">
         <v>78</v>
       </c>
@@ -6246,66 +6510,69 @@
         <v>320</v>
       </c>
       <c r="G34" s="18">
-        <f>ROUND(F34/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J34" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="K34" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="L34" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="M34" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M34" s="9">
+      <c r="N34" s="9">
         <v>9</v>
       </c>
-      <c r="N34" s="20">
+      <c r="O34" s="20">
         <f t="shared" si="10"/>
         <v>648</v>
       </c>
-      <c r="O34" s="25" t="s">
+      <c r="P34" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P34" s="24">
-        <v>0</v>
-      </c>
       <c r="Q34" s="24">
-        <f>4*36*P34</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="20">
+        <v>0</v>
+      </c>
+      <c r="R34" s="24">
+        <f>4*36*Q34</f>
+        <v>0</v>
+      </c>
+      <c r="S34" s="20">
         <f t="shared" si="12"/>
         <v>648</v>
       </c>
-      <c r="S34" s="33">
+      <c r="T34" s="29">
         <v>676</v>
       </c>
-      <c r="T34" s="9" t="s">
+      <c r="U34" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U34" s="9"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20" t="str">
-        <f>IF(OR(U34="",V34=""),"",U34*V34)</f>
-        <v/>
-      </c>
+      <c r="V34" s="9"/>
+      <c r="W34" s="20"/>
       <c r="X34" s="20" t="str">
-        <f>IF(OR(R34="",W34=""),"",R34-W34)</f>
-        <v/>
-      </c>
-      <c r="Y34" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y34" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z34" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="29">
+    <row r="35" spans="1:26" ht="26.4">
       <c r="A35" s="6" t="s">
         <v>78</v>
       </c>
@@ -6325,66 +6592,69 @@
         <v>80</v>
       </c>
       <c r="G35" s="18">
-        <f>ROUND(F35/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>100</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="K35" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K35" s="8" t="s">
+      <c r="L35" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="M35" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M35" s="9">
+      <c r="N35" s="9">
         <v>3</v>
       </c>
-      <c r="N35" s="20">
-        <f>72*M35</f>
+      <c r="O35" s="20">
+        <f>72*N35</f>
         <v>216</v>
       </c>
-      <c r="O35" s="25" t="s">
+      <c r="P35" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P35" s="24">
-        <v>0</v>
-      </c>
       <c r="Q35" s="24">
-        <f t="shared" ref="Q35:Q38" si="15">4*36*P35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="20">
-        <f>N35</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="24">
+        <f t="shared" ref="R35:R38" si="18">4*36*Q35</f>
+        <v>0</v>
+      </c>
+      <c r="S35" s="20">
+        <f>O35</f>
         <v>216</v>
       </c>
-      <c r="S35" s="33">
+      <c r="T35" s="29">
         <v>273</v>
       </c>
-      <c r="T35" s="9" t="s">
+      <c r="U35" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="9"/>
-      <c r="V35" s="20"/>
-      <c r="W35" s="20" t="str">
-        <f>IF(OR(U35="",V35=""),"",U35*V35)</f>
-        <v/>
-      </c>
+      <c r="V35" s="9"/>
+      <c r="W35" s="20"/>
       <c r="X35" s="20" t="str">
-        <f>IF(OR(R35="",W35=""),"",R35-W35)</f>
-        <v/>
-      </c>
-      <c r="Y35" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y35" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z35" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="29">
+    <row r="36" spans="1:26" ht="26.4">
       <c r="A36" s="6" t="s">
         <v>78</v>
       </c>
@@ -6404,66 +6674,69 @@
         <v>320</v>
       </c>
       <c r="G36" s="18">
-        <f>ROUND(F36/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J36" s="8" t="s">
+      <c r="K36" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="K36" s="8" t="s">
+      <c r="L36" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="M36" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M36" s="9">
+      <c r="N36" s="9">
         <v>8</v>
       </c>
-      <c r="N36" s="20">
+      <c r="O36" s="20">
         <f t="shared" si="10"/>
         <v>576</v>
       </c>
-      <c r="O36" s="25" t="s">
+      <c r="P36" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P36" s="24">
-        <v>0</v>
-      </c>
       <c r="Q36" s="24">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R36" s="20">
+        <v>0</v>
+      </c>
+      <c r="R36" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="20">
         <f t="shared" si="12"/>
         <v>576</v>
       </c>
-      <c r="S36" s="33">
+      <c r="T36" s="29">
         <v>622</v>
       </c>
-      <c r="T36" s="9" t="s">
+      <c r="U36" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U36" s="9"/>
-      <c r="V36" s="20"/>
-      <c r="W36" s="20" t="str">
-        <f>IF(OR(U36="",V36=""),"",U36*V36)</f>
-        <v/>
-      </c>
+      <c r="V36" s="9"/>
+      <c r="W36" s="20"/>
       <c r="X36" s="20" t="str">
-        <f>IF(OR(R36="",W36=""),"",R36-W36)</f>
-        <v/>
-      </c>
-      <c r="Y36" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y36" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z36" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="29">
+    <row r="37" spans="1:26" ht="26.4">
       <c r="A37" s="6" t="s">
         <v>78</v>
       </c>
@@ -6483,66 +6756,69 @@
         <v>80</v>
       </c>
       <c r="G37" s="18">
-        <f>ROUND(F37/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>100</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="J37" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="K37" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K37" s="8" t="s">
+      <c r="L37" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L37" s="9" t="s">
+      <c r="M37" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M37" s="9">
+      <c r="N37" s="9">
         <v>1</v>
       </c>
-      <c r="N37" s="20">
+      <c r="O37" s="20">
         <f t="shared" si="10"/>
         <v>72</v>
       </c>
-      <c r="O37" s="25" t="s">
+      <c r="P37" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P37" s="24">
-        <v>0</v>
-      </c>
       <c r="Q37" s="24">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R37" s="20">
+        <v>0</v>
+      </c>
+      <c r="R37" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="20">
         <f t="shared" si="12"/>
         <v>72</v>
       </c>
-      <c r="S37" s="33">
+      <c r="T37" s="29">
         <v>136</v>
       </c>
-      <c r="T37" s="9" t="s">
+      <c r="U37" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U37" s="9"/>
-      <c r="V37" s="20"/>
-      <c r="W37" s="20" t="str">
-        <f>IF(OR(U37="",V37=""),"",U37*V37)</f>
-        <v/>
-      </c>
+      <c r="V37" s="9"/>
+      <c r="W37" s="20"/>
       <c r="X37" s="20" t="str">
-        <f>IF(OR(R37="",W37=""),"",R37-W37)</f>
-        <v/>
-      </c>
-      <c r="Y37" s="10" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y37" s="20" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z37" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="29">
+    <row r="38" spans="1:26" ht="26.4">
       <c r="A38" s="11" t="s">
         <v>78</v>
       </c>
@@ -6562,110 +6838,97 @@
         <v>320</v>
       </c>
       <c r="G38" s="19">
-        <f>ROUND(F38/0.8,0)</f>
+        <f t="shared" si="15"/>
         <v>400</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="J38" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="K38" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="K38" s="13" t="s">
+      <c r="L38" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="M38" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="M38" s="14">
+      <c r="N38" s="14">
         <v>8</v>
       </c>
-      <c r="N38" s="20">
+      <c r="O38" s="20">
         <f t="shared" si="10"/>
         <v>576</v>
       </c>
-      <c r="O38" s="25" t="s">
+      <c r="P38" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="P38" s="24">
-        <v>0</v>
-      </c>
       <c r="Q38" s="24">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="R38" s="20">
+        <v>0</v>
+      </c>
+      <c r="R38" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="20">
         <f t="shared" si="12"/>
         <v>576</v>
       </c>
-      <c r="S38" s="33">
+      <c r="T38" s="29">
         <v>458</v>
       </c>
-      <c r="T38" s="14" t="s">
+      <c r="U38" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="U38" s="14"/>
-      <c r="V38" s="21"/>
-      <c r="W38" s="21" t="str">
-        <f>IF(OR(U38="",V38=""),"",U38*V38)</f>
-        <v/>
-      </c>
+      <c r="V38" s="14"/>
+      <c r="W38" s="21"/>
       <c r="X38" s="21" t="str">
-        <f>IF(OR(R38="",W38=""),"",R38-W38)</f>
-        <v/>
-      </c>
-      <c r="Y38" s="15" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y38" s="21" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Z38" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
-      <c r="L39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="32"/>
-    </row>
-    <row r="40" spans="1:25">
-      <c r="L40" s="31"/>
-      <c r="O40" s="32"/>
-      <c r="P40" s="32"/>
-    </row>
-    <row r="41" spans="1:25">
-      <c r="L41" s="31"/>
-      <c r="O41" s="32"/>
-      <c r="P41" s="32"/>
-    </row>
-    <row r="42" spans="1:25">
-      <c r="L42" s="32"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-    </row>
-    <row r="43" spans="1:25">
-      <c r="L43" s="32"/>
-    </row>
-    <row r="44" spans="1:25">
-      <c r="L44" s="32"/>
+    <row r="39" spans="1:26">
+      <c r="M39" s="7"/>
+      <c r="P39" s="7"/>
+    </row>
+    <row r="40" spans="1:26">
+      <c r="M40" s="7"/>
+    </row>
+    <row r="41" spans="1:26">
+      <c r="M41" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A1:Z1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="S4:S23">
+  <conditionalFormatting sqref="T4:T23">
     <cfRule type="expression" dxfId="3" priority="3">
-      <formula>$S4&gt;=$F4</formula>
+      <formula>$T4&gt;=$F4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="4">
-      <formula>$S4&lt;$F4</formula>
+      <formula>$T4&lt;$F4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S25">
+  <conditionalFormatting sqref="T25">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$S25&gt;=$F25</formula>
+      <formula>$T25&gt;=$F25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$S25&lt;$F25</formula>
+      <formula>$T25&lt;$F25</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6676,7 +6939,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -6685,18 +6948,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-    </row>
-    <row r="2" spans="1:8" ht="32">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+    </row>
+    <row r="2" spans="1:8" ht="27.6">
       <c r="A2" s="1" t="s">
         <v>148</v>
       </c>
@@ -6722,7 +6985,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="32">
+    <row r="3" spans="1:8" ht="27.6">
       <c r="A3" s="2" t="s">
         <v>69</v>
       </c>
@@ -6749,7 +7012,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="32">
+    <row r="4" spans="1:8" ht="27.6">
       <c r="A4" s="2" t="s">
         <v>158</v>
       </c>
@@ -6776,7 +7039,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>122</v>
       </c>
@@ -6803,7 +7066,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16">
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>60</v>
       </c>
@@ -6830,7 +7093,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16">
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -6857,7 +7120,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16">
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>107</v>
       </c>
@@ -6884,7 +7147,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>170</v>
       </c>
@@ -6911,7 +7174,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="32">
+    <row r="10" spans="1:8" ht="27.6">
       <c r="A10" s="2" t="s">
         <v>174</v>
       </c>
@@ -6938,7 +7201,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16">
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>176</v>
       </c>
@@ -6965,7 +7228,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="16">
+    <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
         <v>179</v>
       </c>
